--- a/src/test/resources/codechgfile.text.xlsx
+++ b/src/test/resources/codechgfile.text.xlsx
@@ -34,7 +34,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -91,47 +91,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0901691</t>
+          <t xml:space="preserve">0852083</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가상자산거래소（코인원）　　　</t>
+          <t xml:space="preserve">한강금고장승배기지점　　　　　</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6288 6000 </t>
+          <t xml:space="preserve">02   822  9712 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6288 6000 </t>
+          <t xml:space="preserve">02   823  4041 </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">06925 </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260922</t>
+          <t xml:space="preserve">20260923</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동작구　상도로　１９５　（노량진동，　힐스테이트　장승배기역）　Ｂ１０５호　　　　　　　</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -143,47 +143,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0065786</t>
+          <t xml:space="preserve">0901691</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">서초중앙（점）　　　　　　　　</t>
+          <t xml:space="preserve">가상자산거래소（코인원）　　　</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   598  9282 </t>
+          <t xml:space="preserve">02   6288 6000 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   598  9284 </t>
+          <t xml:space="preserve">02   6288 6000 </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06641 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260922</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　사임당로　８６　（서초동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -200,32 +200,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0072232</t>
+          <t xml:space="preserve">0065786</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가락동금융센터　　　　　　　　</t>
+          <t xml:space="preserve">서초중앙（점）　　　　　　　　</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6425 0961 </t>
+          <t xml:space="preserve">02   598  9282 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   449  0965 </t>
+          <t xml:space="preserve">02   598  9284 </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">05699 </t>
+          <t xml:space="preserve">06641 </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -235,7 +235,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　양재대로　９３２，　가락몰　관리업무동　１층　（가락동）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　사임당로　８６　（서초동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -252,32 +252,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101035</t>
+          <t xml:space="preserve">0072232</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">화정역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">가락동금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  973  8100 </t>
+          <t xml:space="preserve">02   6425 0961 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  973  8104 </t>
+          <t xml:space="preserve">02   449  0965 </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10500 </t>
+          <t xml:space="preserve">05699 </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -287,7 +287,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　덕양구　화신로２６０번길　６６　（화정동）　한빛하이죤　２층　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　양재대로　９３２，　가락몰　관리업무동　１층　（가락동）　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111083</t>
+          <t xml:space="preserve">0101035</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -314,22 +314,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">남양주시（지부）　　　　　　　</t>
+          <t xml:space="preserve">화정역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  563  5991 </t>
+          <t xml:space="preserve">031  973  8100 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  8524 </t>
+          <t xml:space="preserve">031  973  8104 </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">10500 </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -339,7 +339,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로３６번길　２１－２　（다산동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　덕양구　화신로２６０번길　６６　（화정동）　한빛하이죤　２층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -356,7 +356,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113007</t>
+          <t xml:space="preserve">0111083</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -366,22 +366,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">도안동로　　　　　　　　　　　</t>
+          <t xml:space="preserve">남양주시（지부）　　　　　　　</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">042  823  1922 </t>
+          <t xml:space="preserve">031  563  5991 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">042  823  1928 </t>
+          <t xml:space="preserve">031  566  8524 </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">34192 </t>
+          <t xml:space="preserve">12284 </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -391,7 +391,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">대전광역시　유성구　원신흥로　１２２－４　（원신흥동）　레이크빌딩　Ｉ，　２층　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　남양주시　다산지금로３６번길　２１－２　（다산동）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -408,32 +408,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135111</t>
+          <t xml:space="preserve">0113007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">오수관촌　신평　　　　　　　　</t>
+          <t xml:space="preserve">도안동로　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  643  7121 </t>
+          <t xml:space="preserve">042  823  1922 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  643  0065 </t>
+          <t xml:space="preserve">042  823  1928 </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">55911 </t>
+          <t xml:space="preserve">34192 </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -443,7 +443,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　임실군　신평면　석등슬치로　３６５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대전광역시　유성구　원신흥로　１２２－４　（원신흥동）　레이크빌딩　Ｉ，　２층　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -455,37 +455,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233822</t>
+          <t xml:space="preserve">0135111</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">상도동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">오수관촌　신평　　　　　　　　</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   823  2261 </t>
+          <t xml:space="preserve">063  643  7121 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   822  3196 </t>
+          <t xml:space="preserve">063  643  0065 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">156030</t>
+          <t xml:space="preserve">55911 </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -495,49 +495,49 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　동작구상도동３２４의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　임실군　신평면　석등슬치로　３６５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233770</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804248</t>
+          <t xml:space="preserve">0233822</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">운정　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">상도동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8071 3100 </t>
+          <t xml:space="preserve">02   823  2261 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8071 3106 </t>
+          <t xml:space="preserve">02   822  3196 </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896 </t>
+          <t xml:space="preserve">156030</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -547,12 +547,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　파주시　와석순환로５１５번길　１０　（와동동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　동작구상도동３２４의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0233770</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815402</t>
+          <t xml:space="preserve">0804248</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -574,22 +574,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구칠곡금융센터　　　　　　　</t>
+          <t xml:space="preserve">운정　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  381  1111 </t>
+          <t xml:space="preserve">031  8071 3100 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  311  7020 </t>
+          <t xml:space="preserve">031  8071 3106 </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">41423 </t>
+          <t xml:space="preserve">10896 </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　북구　학정로　４１９　（동천동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　파주시　와석순환로５１５번길　１０　（와동동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -611,37 +611,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2613026</t>
+          <t xml:space="preserve">0815402</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">교보증권　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남고객지원파트　　　　　　　</t>
+          <t xml:space="preserve">대구칠곡금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3771 9000 </t>
+          <t xml:space="preserve">053  381  1111 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3771 9747 </t>
+          <t xml:space="preserve">053  311  7020 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">06160 </t>
+          <t xml:space="preserve">41423 </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　테헤란로　４１９　（삼성동）　강남파이낸스플라자２층　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　북구　학정로　４１９　（동천동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -663,37 +663,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2705808</t>
+          <t xml:space="preserve">2613026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">교보증권　　　　　　</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">정자ＷＭ라운지　　　　　　　　</t>
+          <t xml:space="preserve">강남고객지원파트　　　　　　　</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  697  7950 </t>
+          <t xml:space="preserve">02   3771 9000 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  714  0844 </t>
+          <t xml:space="preserve">02   3771 9747 </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">13562 </t>
+          <t xml:space="preserve">06160 </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　정자일로　１００　（정자동，　미켈란쉐르빌），　２층　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　테헤란로　４１９　（삼성동）　강남파이낸스플라자２층　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -720,42 +720,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0137863</t>
+          <t xml:space="preserve">2705808</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">오수관촌　지사　　　　　　　　</t>
+          <t xml:space="preserve">정자ＷＭ라운지　　　　　　　　</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  642  4008 </t>
+          <t xml:space="preserve">031  697  7950 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  642  4071 </t>
+          <t xml:space="preserve">031  714  0844 </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">55921 </t>
+          <t xml:space="preserve">13562 </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　임실군　지사면　충효로　２４４２　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　정자일로　１００　（정자동，　미켈란쉐르빌），　２층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0151218</t>
+          <t xml:space="preserve">0137863</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">진주동부　초전　　　　　　　　</t>
+          <t xml:space="preserve">오수관촌　지사　　　　　　　　</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1398 </t>
+          <t xml:space="preserve">063  642  4008 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5687 </t>
+          <t xml:space="preserve">063  642  4071 </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">52739 </t>
+          <t xml:space="preserve">55921 </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대신로　４４７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　임실군　지사면　충효로　２４４２　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -819,37 +819,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808435</t>
+          <t xml:space="preserve">0151218</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">소호대출후선지원팀　　　　　　</t>
+          <t xml:space="preserve">진주동부　초전　　　　　　　　</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2002 1111 </t>
+          <t xml:space="preserve">055  755  1398 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2002 2553 </t>
+          <t xml:space="preserve">0503 8880 5687 </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">04523 </t>
+          <t xml:space="preserve">52739 </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중구　을지로　３５　（을지로１가）　하나은행　본점　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대신로　４４７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -871,47 +871,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0808435</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">소호대출후선지원팀　　　　　　</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1926 </t>
+          <t xml:space="preserve">02   2002 1111 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">02   2002 2553 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">04523 </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260917</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　을지로　３５　（을지로１가）　하나은행　본점　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0851026</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청금고가회지점　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   747  2670 </t>
+          <t xml:space="preserve">055  755  1926 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   762  6344 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">03056 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　북촌로　４０　（가회동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -980,42 +980,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156200</t>
+          <t xml:space="preserve">0851026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">영남원예　삼방동　　　　　　　</t>
+          <t xml:space="preserve">삼청금고가회지점　　　　　　　</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  337  0750 </t>
+          <t xml:space="preserve">02   747  2670 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5931 </t>
+          <t xml:space="preserve">02   762  6344 </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">50815 </t>
+          <t xml:space="preserve">03056 </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260916</t>
+          <t xml:space="preserve">20260917</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　김해시　삼안로　２５８　화인아파트　상가　１０２호　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　북촌로　４０　（가회동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185310</t>
+          <t xml:space="preserve">0156200</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1042,32 +1042,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
+          <t xml:space="preserve">영남원예　삼방동　　　　　　　</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">055  337  0750 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">0503 8880 5931 </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">24214 </t>
+          <t xml:space="preserve">50815 </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260916</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　（춘천　아테라더퍼스트）　금호아테라더퍼스트　１０９호</t>
+          <t xml:space="preserve">경상남도　김해시　삼안로　２５８　화인아파트　상가　１０２호　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185323</t>
+          <t xml:space="preserve">0185310</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">안성인삼　매교역　　　　　　　</t>
+          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  000  0000 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">16574 </t>
+          <t xml:space="preserve">24214 </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　효원로　１４６　（세류동，　매교역팰루시드）　근린생활시설　지하　２층　７，</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　（춘천　아테라더퍼스트）　금호아테라더퍼스트　１０９호</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1131,37 +1131,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451044</t>
+          <t xml:space="preserve">0185323</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">안성인삼　매교역　　　　　　　</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   733  2670 </t>
+          <t xml:space="preserve">031  000  0000 </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2670 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">03053 </t>
+          <t xml:space="preserve">16574 </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　삼청로　１０６　（삼청동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　효원로　１４６　（세류동，　매교역팰루시드）　근린생활시설　지하　２층　７，</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0451044</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1198,22 +1198,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">삼청　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  7926 </t>
+          <t xml:space="preserve">02   733  2670 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">02   735  2670 </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">03053 </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　삼청로　１０６　（삼청동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1250,22 +1250,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">055  755  7926 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1292,42 +1292,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0014009</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  240  3700 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  246  9953 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">48400 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　남구　문현금융로　２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">0014805</t>
+          <t xml:space="preserve">0014009</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1354,22 +1354,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">부산　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  8800 114  </t>
+          <t xml:space="preserve">051  240  3700 </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  8800 0290 </t>
+          <t xml:space="preserve">051  246  9953 </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">22333 </t>
+          <t xml:space="preserve">48400 </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　제물포구　인항로　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　남구　문현금융로　２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0015008</t>
+          <t xml:space="preserve">0014805</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">인천　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  2500 114  </t>
+          <t xml:space="preserve">032  8800 114  </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  2500 1110 </t>
+          <t xml:space="preserve">032  8800 0290 </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">16508 </t>
+          <t xml:space="preserve">22333 </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　센트럴타운로　３５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　제물포구　인항로　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0015105</t>
+          <t xml:space="preserve">0015008</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1458,22 +1458,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">경기　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  260  5114 </t>
+          <t xml:space="preserve">031  2500 114  </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  267  5605 </t>
+          <t xml:space="preserve">031  2500 1110 </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">51444 </t>
+          <t xml:space="preserve">16508 </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　성산구　원이대로　６３３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　센트럴타운로　３５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1500,32 +1500,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">0105141</t>
+          <t xml:space="preserve">0015105</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">화성시　（지부）　　　　　　　</t>
+          <t xml:space="preserve">경남　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  369  9000 </t>
+          <t xml:space="preserve">055  260  5114 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  366  7696 </t>
+          <t xml:space="preserve">055  267  5605 </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">18270 </t>
+          <t xml:space="preserve">51444 </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　남양읍　시청로１６０번길　４６－１４　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　성산구　원이대로　６３３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110932</t>
+          <t xml:space="preserve">0105141</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파금융　　　　　　　　　　　</t>
+          <t xml:space="preserve">화성시　（지부）　　　　　　　</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   404  6546 </t>
+          <t xml:space="preserve">031  369  9000 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   404  9783 </t>
+          <t xml:space="preserve">031  366  7696 </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">05702 </t>
+          <t xml:space="preserve">18270 </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　중대로２３길　９　（가락동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　남양읍　시청로１６０번길　４６－１４　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0350462</t>
+          <t xml:space="preserve">0110932</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주　　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">송파금융　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  418  4618 </t>
+          <t xml:space="preserve">02   404  6546 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  418  4625 </t>
+          <t xml:space="preserve">02   404  9783 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">48955 </t>
+          <t xml:space="preserve">05702 </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　해관로　１　（동광동１가），　　　２층　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　중대로２３길　９　（가락동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1651,37 +1651,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878067</t>
+          <t xml:space="preserve">0350462</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">제주　　　　　　　　</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">용인중앙금고　수지금융센터지점</t>
+          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  895  5200 </t>
+          <t xml:space="preserve">051  418  4618 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  895  5204 </t>
+          <t xml:space="preserve">051  418  4625 </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">16871 </t>
+          <t xml:space="preserve">48955 </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　용인시　수지구　현암로　６９　（죽전동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　해관로　１　（동광동１가），　　　２층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1703,47 +1703,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124407</t>
+          <t xml:space="preserve">0878067</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">조치원　시장　　　　　　　　　</t>
+          <t xml:space="preserve">용인중앙금고　수지금융센터지점</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">044  865  2461 </t>
+          <t xml:space="preserve">031  895  5200 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 2955 </t>
+          <t xml:space="preserve">031  895  5204 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">30027 </t>
+          <t xml:space="preserve">16871 </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">세종특별자치시　조치원읍　새내１０길　１２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　용인시　수지구　현암로　６９　（죽전동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0129088</t>
+          <t xml:space="preserve">0124407</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">왕궁농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">조치원　시장　　　　　　　　　</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  832  4008 </t>
+          <t xml:space="preserve">044  865  2461 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 3597 </t>
+          <t xml:space="preserve">0503 8880 2955 </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">54576 </t>
+          <t xml:space="preserve">30027 </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　익산시　왕궁면　흥암１길　２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">세종특별자치시　조치원읍　새내１０길　１２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185284</t>
+          <t xml:space="preserve">0129088</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1822,22 +1822,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">남원축협　조산지점　　　　　　</t>
+          <t xml:space="preserve">왕궁농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  630  1160 </t>
+          <t xml:space="preserve">063  832  4008 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  000  0000 </t>
+          <t xml:space="preserve">0503 8880 3597 </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">55778 </t>
+          <t xml:space="preserve">54576 </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　남원시　요천로　１２７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　왕궁면　흥암１길　２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1864,32 +1864,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0859963</t>
+          <t xml:space="preserve">0185284</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른금고원마루지점　　　　　　</t>
+          <t xml:space="preserve">남원축협　조산지점　　　　　　</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  292  0047 </t>
+          <t xml:space="preserve">063  630  1160 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  291  6797 </t>
+          <t xml:space="preserve">063  000  0000 </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">28792 </t>
+          <t xml:space="preserve">55778 </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북　청주시　서원구　월평로　６９　（분평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　남원시　요천로　１２７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0868556</t>
+          <t xml:space="preserve">0859963</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른금고분평지점　　　　　　　</t>
+          <t xml:space="preserve">푸른금고원마루지점　　　　　　</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  285  6066 </t>
+          <t xml:space="preserve">043  292  0047 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  283  6066 </t>
+          <t xml:space="preserve">043  291  6797 </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">28799 </t>
+          <t xml:space="preserve">28792 </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　서원구　분평로　３２　（분평동）１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충북　청주시　서원구　월평로　６９　（분평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0868556</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1978,22 +1978,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">푸른금고분평지점　　　　　　　</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1926 </t>
+          <t xml:space="preserve">043  285  6066 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">043  283  6066 </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">28799 </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　서원구　분평로　３２　（분평동）１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2020,42 +2020,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0123204</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주농협　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  2481 </t>
+          <t xml:space="preserve">055  755  1926 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  5188 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">37116 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　함창읍　함창시장１길　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0131432</t>
+          <t xml:space="preserve">0123204</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">규암　장암　　　　　　　　　　</t>
+          <t xml:space="preserve">북상주농협　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  834  2280 </t>
+          <t xml:space="preserve">054  541  2481 </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  834  7071 </t>
+          <t xml:space="preserve">054  541  5188 </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">33183 </t>
+          <t xml:space="preserve">37116 </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　부여군　장암면　장암로　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　함창읍　함창시장１길　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0138477</t>
+          <t xml:space="preserve">0131432</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2134,22 +2134,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주　은척　　　　　　　　　</t>
+          <t xml:space="preserve">규암　장암　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  3406 </t>
+          <t xml:space="preserve">041  834  2280 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  6764 </t>
+          <t xml:space="preserve">041  834  7071 </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">37104 </t>
+          <t xml:space="preserve">33183 </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　은척면　성주로　７５４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　부여군　장암면　장암로　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0138480</t>
+          <t xml:space="preserve">0138477</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2186,22 +2186,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주　이안　　　　　　　　　</t>
+          <t xml:space="preserve">북상주　은척　　　　　　　　　</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  5310 </t>
+          <t xml:space="preserve">054  541  3406 </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  0310 </t>
+          <t xml:space="preserve">054  541  6764 </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">37107 </t>
+          <t xml:space="preserve">37104 </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　이안면　양범안룡길　２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　은척면　성주로　７５４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156792</t>
+          <t xml:space="preserve">0138480</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2238,22 +2238,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔탄　구장　　　　　　　　　　</t>
+          <t xml:space="preserve">북상주　이안　　　　　　　　　</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  352  8803 </t>
+          <t xml:space="preserve">054  541  5310 </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  352  8126 </t>
+          <t xml:space="preserve">054  541  0310 </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">18529 </t>
+          <t xml:space="preserve">37107 </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　팔탄면　시청로　９３４－５　Ａ동　２０１호　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　이안면　양범안룡길　２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2280,42 +2280,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0072850</t>
+          <t xml:space="preserve">0156792</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">청라지점　　　　　　　　　　　</t>
+          <t xml:space="preserve">팔탄　구장　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  569  4960 </t>
+          <t xml:space="preserve">031  352  8803 </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  569  4963 </t>
+          <t xml:space="preserve">031  352  8126 </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">22736 </t>
+          <t xml:space="preserve">18529 </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서해구　청라라임로　７１，　２０４호（청라동，　진영메디피아）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　팔탄면　시청로　９３４－５　Ａ동　２０１호　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2332,32 +2332,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451028</t>
+          <t xml:space="preserve">0072850</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">광화문　　　　　　　　　　　　</t>
+          <t xml:space="preserve">청라지점　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2188 </t>
+          <t xml:space="preserve">032  569  4960 </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2186 </t>
+          <t xml:space="preserve">032  569  4963 </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">03040 </t>
+          <t xml:space="preserve">22736 </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　자하문로９길　９　（통인동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서해구　청라라임로　７１，　２０４호（청라동，　진영메디피아）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0859109</t>
+          <t xml:space="preserve">0451028</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2394,22 +2394,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">강릉솔향금고교동지점　　　　　</t>
+          <t xml:space="preserve">광화문　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  643  3843 </t>
+          <t xml:space="preserve">02   735  2188 </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  643  3369 </t>
+          <t xml:space="preserve">02   735  2186 </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">25506 </t>
+          <t xml:space="preserve">03040 </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　강릉시　강릉대로　１４５　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　자하문로９길　９　（통인동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2436,42 +2436,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0032861</t>
+          <t xml:space="preserve">0859109</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">진주상평（지）　　　　　　　　</t>
+          <t xml:space="preserve">강릉솔향금고교동지점　　　　　</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  758  0665 </t>
+          <t xml:space="preserve">033  643  3843 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0286 </t>
+          <t xml:space="preserve">033  643  3369 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">52775 </t>
+          <t xml:space="preserve">25506 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대신로　２１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　강릉시　강릉대로　１４５　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2488,32 +2488,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0100816</t>
+          <t xml:space="preserve">0032861</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">메트로팔레스　　　　　　　　　</t>
+          <t xml:space="preserve">진주상평（지）　　　　　　　　</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  746  4588 </t>
+          <t xml:space="preserve">055  758  0665 </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  746  4582 </t>
+          <t xml:space="preserve">0505 075  0286 </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">42038 </t>
+          <t xml:space="preserve">52775 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　수성구　화랑로　５０　자삼빌딩　１층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대신로　２１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101488</t>
+          <t xml:space="preserve">0100816</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">이수역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">메트로팔레스　　　　　　　　　</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   599  5731 </t>
+          <t xml:space="preserve">053  746  4588 </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   599  5735 </t>
+          <t xml:space="preserve">053  746  4582 </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">06567 </t>
+          <t xml:space="preserve">42038 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　동작대로　１３２　（방배동），　안석빌딩　１층　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　수성구　화랑로　５０　자삼빌딩　１층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110589</t>
+          <t xml:space="preserve">0101488</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2602,22 +2602,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">논현남　　　　　　　　　　　　</t>
+          <t xml:space="preserve">이수역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   561  2836 </t>
+          <t xml:space="preserve">02   599  5731 </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   561  2835 </t>
+          <t xml:space="preserve">02   599  5735 </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">06122 </t>
+          <t xml:space="preserve">06567 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　봉은사로　１５１　（논현동），　분데스언주　４층　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　동작대로　１３２　（방배동），　안석빌딩　１층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110725</t>
+          <t xml:space="preserve">0110589</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">면목역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">논현남　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   494  1596 </t>
+          <t xml:space="preserve">02   561  2836 </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2207 0207 </t>
+          <t xml:space="preserve">02   561  2835 </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02160 </t>
+          <t xml:space="preserve">06122 </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중랑구　면목로　４３２　（면목동）　３층　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　봉은사로　１５１　（논현동），　분데스언주　４층　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2696,32 +2696,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0200732</t>
+          <t xml:space="preserve">0110725</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">영동금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">면목역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   546  0911 </t>
+          <t xml:space="preserve">02   494  1596 </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3073 </t>
+          <t xml:space="preserve">02   2207 0207 </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">135766</t>
+          <t xml:space="preserve">02160 </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　학동로　４０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중랑구　면목로　４３２　（면목동）　３층　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0200949</t>
+          <t xml:space="preserve">0200732</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2758,22 +2758,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남교보타워금융센터　　　　　</t>
+          <t xml:space="preserve">영동금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3481 5041 </t>
+          <t xml:space="preserve">02   546  0911 </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3094 </t>
+          <t xml:space="preserve">0505 001  3073 </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">137920</t>
+          <t xml:space="preserve">135766</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　강남대로　４６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　학동로　４０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201032</t>
+          <t xml:space="preserve">0200949</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">여의도금융센터　　　　　　　　</t>
+          <t xml:space="preserve">강남교보타워금융센터　　　　　</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   785  7100 </t>
+          <t xml:space="preserve">02   3481 5041 </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3103 </t>
+          <t xml:space="preserve">0505 001  3094 </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">150714</t>
+          <t xml:space="preserve">137920</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로８길　１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　강남대로　４６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201430</t>
+          <t xml:space="preserve">0201032</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">여의도중앙금융센터　　　　　　</t>
+          <t xml:space="preserve">여의도금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   783  4101 </t>
+          <t xml:space="preserve">02   785  7100 </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3143 </t>
+          <t xml:space="preserve">0505 001  3103 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">07327 </t>
+          <t xml:space="preserve">150714</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　여의나루로　７１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로８길　１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201980</t>
+          <t xml:space="preserve">0201430</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2914,22 +2914,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">사상금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">여의도중앙금융센터　　　　　　</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  322  7200 </t>
+          <t xml:space="preserve">02   783  4101 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3198 </t>
+          <t xml:space="preserve">0505 001  3143 </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">617060</t>
+          <t xml:space="preserve">07327 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　사상구　감전１동　１５２－２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　여의나루로　７１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0202031</t>
+          <t xml:space="preserve">0201980</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2966,22 +2966,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">양재중앙금융센터　　　　　　　</t>
+          <t xml:space="preserve">사상금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   589  1900 </t>
+          <t xml:space="preserve">051  322  7200 </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3203 </t>
+          <t xml:space="preserve">0505 001  3198 </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">137131</t>
+          <t xml:space="preserve">617060</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　양재동　２７５－１외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산　사상구　감전１동　１５２－２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0205669</t>
+          <t xml:space="preserve">0202031</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3018,22 +3018,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">양재중앙금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2691 2141 </t>
+          <t xml:space="preserve">02   589  1900 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3566 </t>
+          <t xml:space="preserve">0505 001  3203 </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">07714 </t>
+          <t xml:space="preserve">137131</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강서구　강서로　１７９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　양재동　２７５－１외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0207421</t>
+          <t xml:space="preserve">0205669</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3070,22 +3070,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">역삼역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   565  8671 </t>
+          <t xml:space="preserve">02   2691 2141 </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3742 </t>
+          <t xml:space="preserve">0505 001  3566 </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">135080</t>
+          <t xml:space="preserve">07714 </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　역삼동　７２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강서구　강서로　１７９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208802</t>
+          <t xml:space="preserve">0207421</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">교대역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">역삼역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   586  2001 </t>
+          <t xml:space="preserve">02   565  8671 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3880 </t>
+          <t xml:space="preserve">0505 001  3742 </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">137070</t>
+          <t xml:space="preserve">135080</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　서초동　１５７７－４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　역삼동　７２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3159,37 +3159,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0501046</t>
+          <t xml:space="preserve">0208802</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">조은　　　　여수（지）　　　　</t>
+          <t xml:space="preserve">교대역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  660  0114 </t>
+          <t xml:space="preserve">02   586  2001 </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  666  0107 </t>
+          <t xml:space="preserve">0505 001  3880 </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">59734 </t>
+          <t xml:space="preserve">137070</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3199,49 +3199,49 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　여수시　중앙로　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　서초동　１５７７－４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0500241</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877822</t>
+          <t xml:space="preserve">0501046</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">산남금고　중앙지점　　　　　　</t>
+          <t xml:space="preserve">조은　　　　여수（지）　　　　</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  733  2250 </t>
+          <t xml:space="preserve">061  660  0114 </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  733  2252 </t>
+          <t xml:space="preserve">061  666  0107 </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">63591 </t>
+          <t xml:space="preserve">59734 </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　서귀포시　중앙로　４２　（서귀동）　산남금고　중앙지점　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　여수시　중앙로　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0500241</t>
         </is>
       </c>
     </row>
@@ -3268,42 +3268,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135360</t>
+          <t xml:space="preserve">0877822</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">북부　율어　　　　　　　　　　</t>
+          <t xml:space="preserve">산남금고　중앙지점　　　　　　</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  852  7013 </t>
+          <t xml:space="preserve">064  733  2250 </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  852  7014 </t>
+          <t xml:space="preserve">064  733  2252 </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">59409 </t>
+          <t xml:space="preserve">63591 </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　보성군　율어면　율어로　５６１　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　서귀포시　중앙로　４２　（서귀동）　산남금고　중앙지점　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0171816</t>
+          <t xml:space="preserve">0135360</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">고양　원흥　　　　　　　　　　</t>
+          <t xml:space="preserve">북부　율어　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  966  6104 </t>
+          <t xml:space="preserve">061  852  7013 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  967  6114 </t>
+          <t xml:space="preserve">061  852  7014 </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">10564 </t>
+          <t xml:space="preserve">59409 </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　덕양구　권율대로　６７２　１층（원흥역봄오피스텔상가）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　보성군　율어면　율어로　５６１　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3372,32 +3372,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233479</t>
+          <t xml:space="preserve">0171816</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
+          <t xml:space="preserve">고양　원흥　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  661  7289 </t>
+          <t xml:space="preserve">031  966  6104 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  661  7082 </t>
+          <t xml:space="preserve">031  967  6114 </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">48931 </t>
+          <t xml:space="preserve">10564 </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　대청로　１３５　（중앙동３가）　７층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　덕양구　권율대로　６７２　１층（원흥역봄오피스텔상가）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0233479</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">051  661  7289 </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">051  661  7082 </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">48931 </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　대청로　１３５　（중앙동３가）　７층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878038</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　금산지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  7750 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  763  3080 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">52630 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878041</t>
+          <t xml:space="preserve">0878038</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3590,22 +3590,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　대곡지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　금산지점　　　　　</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  744  2690 </t>
+          <t xml:space="preserve">055  761  7750 </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  746  7046 </t>
+          <t xml:space="preserve">055  763  3080 </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">52607 </t>
+          <t xml:space="preserve">52630 </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878054</t>
+          <t xml:space="preserve">0878041</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3642,22 +3642,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　문산지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　대곡지점　　　　　</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  5379 </t>
+          <t xml:space="preserve">055  744  2690 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  9990 </t>
+          <t xml:space="preserve">055  746  7046 </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">52832 </t>
+          <t xml:space="preserve">52607 </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3679,47 +3679,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233479</t>
+          <t xml:space="preserve">0878054</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
+          <t xml:space="preserve">참진주금고　문산지점　　　　　</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2146 6253 </t>
+          <t xml:space="preserve">055  761  5379 </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3431 3839 </t>
+          <t xml:space="preserve">055  761  9990 </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">05571 </t>
+          <t xml:space="preserve">52832 </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260903</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　올림픽로４길　４０　（잠실동）　우성　Ｂ상가　１층　ＳＣ제일은행　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3731,47 +3731,47 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124041</t>
+          <t xml:space="preserve">0233479</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">서하남　감북　　　　　　　　　</t>
+          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   482  0365 </t>
+          <t xml:space="preserve">02   2146 6253 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   482  0367 </t>
+          <t xml:space="preserve">02   3431 3839 </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990 </t>
+          <t xml:space="preserve">05571 </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260903</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　하남시　서하남로　１２４　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로４길　４０　（잠실동）　우성　Ｂ상가　１층　ＳＣ제일은행　　　　　　　　</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124504</t>
+          <t xml:space="preserve">0124041</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">성환농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">서하남　감북　　　　　　　　　</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  581  2911 </t>
+          <t xml:space="preserve">02   482  0365 </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  582  3261 </t>
+          <t xml:space="preserve">02   482  0367 </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">31022 </t>
+          <t xml:space="preserve">12990 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　성환읍　천안대로　２１２２－１５　２층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　하남시　서하남로　１２４　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3840,32 +3840,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0710934</t>
+          <t xml:space="preserve">0124504</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울대학교우체국　　　　　　　</t>
+          <t xml:space="preserve">성환농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   889  0205 </t>
+          <t xml:space="preserve">041  581  2911 </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   878  8216 </t>
+          <t xml:space="preserve">041  582  3261 </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">08826 </t>
+          <t xml:space="preserve">31022 </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　관악구　관악로　１　（신림동，서울대학교）　두레문예관　６７동　１０５호　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　천안시　서북구　성환읍　천안대로　２１２２－１５　２층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0720704</t>
+          <t xml:space="preserve">0710934</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3902,22 +3902,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천신북우체국　　　　　　　　</t>
+          <t xml:space="preserve">서울대학교우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  243  9957 </t>
+          <t xml:space="preserve">02   889  0205 </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  243  1401 </t>
+          <t xml:space="preserve">02   878  8216 </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">24206 </t>
+          <t xml:space="preserve">08826 </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　율문１길　１６－４　（신북읍，춘천신북우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　관악구　관악로　１　（신림동，서울대학교）　두레문예관　６７동　１０５호　　　　　　　　</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0728913</t>
+          <t xml:space="preserve">0720704</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3954,22 +3954,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항대이동우체국　　　　　　　</t>
+          <t xml:space="preserve">춘천신북우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  278  1921 </t>
+          <t xml:space="preserve">033  243  9957 </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  278  1923 </t>
+          <t xml:space="preserve">033  243  1401 </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">37684 </t>
+          <t xml:space="preserve">24206 </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　남구　대이로４１번길　１８　포항대이동우체국　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　율문１길　１６－４　（신북읍，춘천신북우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0730147</t>
+          <t xml:space="preserve">0728913</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">보은우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">포항대이동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  544  2005 </t>
+          <t xml:space="preserve">054  278  1921 </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  542  3589 </t>
+          <t xml:space="preserve">054  278  1923 </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">28943 </t>
+          <t xml:space="preserve">37684 </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　보은군　보은로　１３５　（보은읍）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　남구　대이로４１번길　１８　포항대이동우체국　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0734486</t>
+          <t xml:space="preserve">0730147</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4058,22 +4058,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">보은우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  629  2572 </t>
+          <t xml:space="preserve">043  544  2005 </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  622  8975 </t>
+          <t xml:space="preserve">043  542  3589 </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">31158 </t>
+          <t xml:space="preserve">28943 </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　백석３로　１０５　（백석동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　보은군　보은로　１３５　（보은읍）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0739371</t>
+          <t xml:space="preserve">0734486</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">신제주우체국　　　　　　　　　</t>
+          <t xml:space="preserve">천안우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  746  0004 </t>
+          <t xml:space="preserve">041  629  2572 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  747  0195 </t>
+          <t xml:space="preserve">041  622  8975 </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">63122 </t>
+          <t xml:space="preserve">31158 </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　제주시　선덕로　５　（연동　３１３－４２，　신제주우체국）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　천안시　서북구　백석３로　１０５　（백석동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0740470</t>
+          <t xml:space="preserve">0739371</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4162,22 +4162,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">무주무풍우체국　　　　　　　　</t>
+          <t xml:space="preserve">신제주우체국　　　　　　　　　</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  324  4400 </t>
+          <t xml:space="preserve">064  746  0004 </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  324  1630 </t>
+          <t xml:space="preserve">064  747  0195 </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">55559 </t>
+          <t xml:space="preserve">63122 </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　무주군　현내로　１６５－１０　（무풍면）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　선덕로　５　（연동　３１３－４２，　신제주우체국）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">0741314</t>
+          <t xml:space="preserve">0740470</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">완주상관우체국　　　　　　　　</t>
+          <t xml:space="preserve">무주무풍우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  282  5000 </t>
+          <t xml:space="preserve">063  324  4400 </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  232  0640 </t>
+          <t xml:space="preserve">063  324  1630 </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">55359 </t>
+          <t xml:space="preserve">55559 </t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　완주군　신리로　１０９　（상관면，상관면주민자치센터）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　무주군　현내로　１６５－１０　（무풍면）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">0744159</t>
+          <t xml:space="preserve">0741314</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">돌산우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">완주상관우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  644  1100 </t>
+          <t xml:space="preserve">063  282  5000 </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  644  1316 </t>
+          <t xml:space="preserve">063  232  0640 </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">59777 </t>
+          <t xml:space="preserve">55359 </t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　방답길　５５－１　（돌산읍，돌산우체국）　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　완주군　신리로　１０９　（상관면，상관면주민자치센터）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0745860</t>
+          <t xml:space="preserve">0744159</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">해남마산우체국　　　　　　　　</t>
+          <t xml:space="preserve">돌산우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  532  5201 </t>
+          <t xml:space="preserve">061  644  1100 </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  534  2654 </t>
+          <t xml:space="preserve">061  644  1316 </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">59020 </t>
+          <t xml:space="preserve">59777 </t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　해남군　마산로　４４８　（마산면，해남마산우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　방답길　５５－１　（돌산읍，돌산우체국）　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">0745996</t>
+          <t xml:space="preserve">0745860</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4370,22 +4370,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">도덕우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">해남마산우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  843  0204 </t>
+          <t xml:space="preserve">061  532  5201 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 005  1865 </t>
+          <t xml:space="preserve">061  534  2654 </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">59546 </t>
+          <t xml:space="preserve">59020 </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　고흥군　고흥로　４５３　（도덕면，도덕우체국）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　해남군　마산로　４４８　（마산면，해남마산우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746296</t>
+          <t xml:space="preserve">0745996</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4422,22 +4422,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">서삼우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">도덕우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  394  0214 </t>
+          <t xml:space="preserve">061  843  0204 </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  393  1391 </t>
+          <t xml:space="preserve">0505 005  1865 </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">57232 </t>
+          <t xml:space="preserve">59546 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　장성군　축령로　３６５　（서삼면，서삼우체국）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　고흥군　고흥로　４５３　（도덕면，도덕우체국）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746911</t>
+          <t xml:space="preserve">0746296</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4474,22 +4474,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">여수봉산동우체국　　　　　　　</t>
+          <t xml:space="preserve">서삼우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  6105 </t>
+          <t xml:space="preserve">061  394  0214 </t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  1305 </t>
+          <t xml:space="preserve">061  393  1391 </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">59763 </t>
+          <t xml:space="preserve">57232 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　어항로　３７　（봉산동，여수봉산동우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　장성군　축령로　３６５　（서삼면，서삼우체국）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4516,42 +4516,42 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118028</t>
+          <t xml:space="preserve">0746911</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">창동아레나　　　　　　　　　　</t>
+          <t xml:space="preserve">여수봉산동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7644 </t>
+          <t xml:space="preserve">061  643  6105 </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7648 </t>
+          <t xml:space="preserve">061  642  1305 </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">01414 </t>
+          <t xml:space="preserve">59763 </t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　어항로　３７　（봉산동，여수봉산동우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">0172899</t>
+          <t xml:space="preserve">0118028</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북대구낙농　효자　　　　　　</t>
+          <t xml:space="preserve">창동아레나　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  283  9051 </t>
+          <t xml:space="preserve">02   990  7644 </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  283  9054 </t>
+          <t xml:space="preserve">02   990  7648 </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">37836 </t>
+          <t xml:space="preserve">01414 </t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　남구　효성로　３７　（효자동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4620,32 +4620,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505576</t>
+          <t xml:space="preserve">0172899</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">라인　　　　영업부　　　　　　</t>
+          <t xml:space="preserve">경북대구낙농　효자　　　　　　</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  223  5506 </t>
+          <t xml:space="preserve">054  283  9051 </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  223  4686 </t>
+          <t xml:space="preserve">054  283  9054 </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">61480 </t>
+          <t xml:space="preserve">37836 </t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　동구　중앙로　１６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　남구　효성로　３７　（효자동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4667,37 +4667,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">0644563</t>
+          <t xml:space="preserve">0505576</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">산림조합　　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">당진시산림조합수청지점　　　　</t>
+          <t xml:space="preserve">라인　　　　영업부　　　　　　</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  970  2105 </t>
+          <t xml:space="preserve">062  223  5506 </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  970  6106 </t>
+          <t xml:space="preserve">062  223  4686 </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">31817 </t>
+          <t xml:space="preserve">61480 </t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　당진시　수청２로　５２　（수청동）　당진시산림조합수청지점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　동구　중앙로　１６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4719,47 +4719,47 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0030614</t>
+          <t xml:space="preserve">0644563</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">산림조합　　　　　　</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">논현역（지）　　　　　　　　　</t>
+          <t xml:space="preserve">당진시산림조합수청지점　　　　</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   548  4156 </t>
+          <t xml:space="preserve">041  970  2105 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0061 </t>
+          <t xml:space="preserve">041  970  6106 </t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">06110 </t>
+          <t xml:space="preserve">31817 </t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　강남대로　５６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　당진시　수청２로　５２　（수청동）　당진시산림조합수청지점　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">0033514</t>
+          <t xml:space="preserve">0030614</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4786,22 +4786,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천서해구청역　　　　　　　　</t>
+          <t xml:space="preserve">논현역（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  561  6231 </t>
+          <t xml:space="preserve">02   548  4156 </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0351 </t>
+          <t xml:space="preserve">0505 075  0061 </t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">22727 </t>
+          <t xml:space="preserve">06110 </t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서해구　서곶로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　강남대로　５６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4828,32 +4828,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113654</t>
+          <t xml:space="preserve">0033514</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">익산시（지부）　　　　　　　　</t>
+          <t xml:space="preserve">인천서해구청역　　　　　　　　</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  835  4100 </t>
+          <t xml:space="preserve">032  561  6231 </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  835  5995 </t>
+          <t xml:space="preserve">0505 075  0351 </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">54545 </t>
+          <t xml:space="preserve">22727 </t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　익산시　무왕로　１０６９　（영등동）　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서해구　서곶로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4880,32 +4880,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">0129101</t>
+          <t xml:space="preserve">0113654</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">광양동부농협　　　　　　　　　</t>
+          <t xml:space="preserve">익산시（지부）　　　　　　　　</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  772  2080 </t>
+          <t xml:space="preserve">063  835  4100 </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  772  5885 </t>
+          <t xml:space="preserve">063  835  5995 </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">57712 </t>
+          <t xml:space="preserve">54545 </t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광양시　진월면　선소중앙길　３８　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　무왕로　１０６９　（영등동）　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4927,37 +4927,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451895</t>
+          <t xml:space="preserve">0129101</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">신촌　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광양동부농협　　　　　　　　　</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   393  8275 </t>
+          <t xml:space="preserve">061  772  2080 </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   364  8275 </t>
+          <t xml:space="preserve">061  772  5885 </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">03776 </t>
+          <t xml:space="preserve">57712 </t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서대문구　연세로　３２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광양시　진월면　선소중앙길　３８　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877039</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456272</t>
+          <t xml:space="preserve">0451895</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉산　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">신촌　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  424  1628 </t>
+          <t xml:space="preserve">02   393  8275 </t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1629 </t>
+          <t xml:space="preserve">02   364  8275 </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">41959 </t>
+          <t xml:space="preserve">03776 </t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　봉산문화길　２８　봉산새마을금고　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서대문구　연세로　３２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877152</t>
+          <t xml:space="preserve">0877039</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456311</t>
+          <t xml:space="preserve">0456272</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5046,22 +5046,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">대신　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">봉산　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  3525 </t>
+          <t xml:space="preserve">053  424  1628 </t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  0939 </t>
+          <t xml:space="preserve">053  422  1629 </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">41927 </t>
+          <t xml:space="preserve">41959 </t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　큰장로２６안길　５　（대신동２６５－５）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　봉산문화길　２８　봉산새마을금고　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877136</t>
+          <t xml:space="preserve">0877152</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456832</t>
+          <t xml:space="preserve">0456311</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5098,22 +5098,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">불로봉무　　　　　　　　　　　</t>
+          <t xml:space="preserve">대신　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  983  6037 </t>
+          <t xml:space="preserve">053  252  3525 </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  981  6037 </t>
+          <t xml:space="preserve">053  256  0939 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">41035 </t>
+          <t xml:space="preserve">41927 </t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　동구　팔공로　１３１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　큰장로２６안길　５　（대신동２６５－５）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877178</t>
+          <t xml:space="preserve">0877136</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0463773</t>
+          <t xml:space="preserve">0456832</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5150,22 +5150,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국인삼공사원주공장　　　　　</t>
+          <t xml:space="preserve">불로봉무　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  747  3070 </t>
+          <t xml:space="preserve">053  983  6037 </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  747  3959 </t>
+          <t xml:space="preserve">053  981  6037 </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">26306 </t>
+          <t xml:space="preserve">41035 </t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원　원주시　소초면　북원로　２９５５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　동구　팔공로　１３１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877084</t>
+          <t xml:space="preserve">0877178</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0465755</t>
+          <t xml:space="preserve">0463773</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일　　　　　　　　　　　</t>
+          <t xml:space="preserve">한국인삼공사원주공장　　　　　</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  244  0321 </t>
+          <t xml:space="preserve">033  747  3070 </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  244  0302 </t>
+          <t xml:space="preserve">033  747  3959 </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">37507 </t>
+          <t xml:space="preserve">26306 </t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북　포항시　북구　죽장면　새마을로　３６２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원　원주시　소초면　북원로　２９５５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877055</t>
+          <t xml:space="preserve">0877084</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860114</t>
+          <t xml:space="preserve">0465755</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5254,22 +5254,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">대신금고대신지점　　　　　　　</t>
+          <t xml:space="preserve">포항제일　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  6833 </t>
+          <t xml:space="preserve">054  244  0321 </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  6834 </t>
+          <t xml:space="preserve">054  244  0302 </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">41929 </t>
+          <t xml:space="preserve">37507 </t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　달구벌대로　１９５５　（대신동１７５１）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북　포항시　북구　죽장면　새마을로　３６２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877149</t>
+          <t xml:space="preserve">0877055</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860923</t>
+          <t xml:space="preserve">0860114</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉산금고중앙지점　　　　　　　</t>
+          <t xml:space="preserve">대신금고대신지점　　　　　　　</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1425 </t>
+          <t xml:space="preserve">053  252  6833 </t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1424 </t>
+          <t xml:space="preserve">053  252  6834 </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">41912 </t>
+          <t xml:space="preserve">41929 </t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　교동３길　２３　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　달구벌대로　１９５５　（대신동１７５１）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877165</t>
+          <t xml:space="preserve">0877149</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0866396</t>
+          <t xml:space="preserve">0860923</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5358,22 +5358,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일금고청하지점　　　　　</t>
+          <t xml:space="preserve">봉산금고중앙지점　　　　　　　</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  232  4931 </t>
+          <t xml:space="preserve">053  422  1425 </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  232  6311 </t>
+          <t xml:space="preserve">053  422  1424 </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">37515 </t>
+          <t xml:space="preserve">41912 </t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북　포항시　북구　청하면　청하로　１９２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　교동３길　２３　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877068</t>
+          <t xml:space="preserve">0877165</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0870447</t>
+          <t xml:space="preserve">0866396</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5410,22 +5410,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">불로봉무금고이시아폴리스지점　</t>
+          <t xml:space="preserve">포항제일금고청하지점　　　　　</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  215  7770 </t>
+          <t xml:space="preserve">054  232  4931 </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  984  7627 </t>
+          <t xml:space="preserve">054  232  6311 </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">41026 </t>
+          <t xml:space="preserve">37515 </t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　동구　팔공로５１길　３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북　포항시　북구　청하면　청하로　１９２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0871815</t>
+          <t xml:space="preserve">0877068</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874650</t>
+          <t xml:space="preserve">0870447</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5462,22 +5462,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일새마을금고초곡지점　　</t>
+          <t xml:space="preserve">불로봉무금고이시아폴리스지점　</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  261  0301 </t>
+          <t xml:space="preserve">053  215  7770 </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  261  0302 </t>
+          <t xml:space="preserve">053  984  7627 </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">37560 </t>
+          <t xml:space="preserve">41026 </t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5487,24 +5487,24 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　북구　흥해읍　초곡지구로　１０７　포항제일금고　초곡지점　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　동구　팔공로５１길　３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877071</t>
+          <t xml:space="preserve">0871815</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0874650</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　상봉지점　　　　　　</t>
+          <t xml:space="preserve">포항제일새마을금고초곡지점　　</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">054  261  0301 </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">054  261  0302 </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">37560 </t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　북구　흥해읍　초곡지구로　１０７　포항제일금고　초곡지점　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877071</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878038</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　금산지점　　　　　　</t>
+          <t xml:space="preserve">상봉금고　상봉지점　　　　　　</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  7750 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  763  3080 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">52630 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878041</t>
+          <t xml:space="preserve">0878038</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5618,22 +5618,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　대곡지점　　　　　　</t>
+          <t xml:space="preserve">상봉금고　금산지점　　　　　　</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  744  2690 </t>
+          <t xml:space="preserve">055  761  7750 </t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  746  7046 </t>
+          <t xml:space="preserve">055  763  3080 </t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">52607 </t>
+          <t xml:space="preserve">52630 </t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878054</t>
+          <t xml:space="preserve">0878041</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5670,22 +5670,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　문산지점　　　　　　</t>
+          <t xml:space="preserve">상봉금고　대곡지점　　　　　　</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  5379 </t>
+          <t xml:space="preserve">055  744  2690 </t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  9990 </t>
+          <t xml:space="preserve">055  746  7046 </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">52832 </t>
+          <t xml:space="preserve">52607 </t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878012</t>
+          <t xml:space="preserve">0878054</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5722,32 +5722,32 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울숲금고　왕심리중앙지점　　</t>
+          <t xml:space="preserve">상봉금고　문산지점　　　　　　</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2292 0894 </t>
+          <t xml:space="preserve">055  761  5379 </t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2295 6243 </t>
+          <t xml:space="preserve">055  761  9990 </t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">04709 </t>
+          <t xml:space="preserve">52832 </t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260828</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　성동구　무학로６길　５０　（도선동，　성동삼성쉐르빌）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5759,47 +5759,47 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0172051</t>
+          <t xml:space="preserve">0878012</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">남양주축산농협　　　　　　　　</t>
+          <t xml:space="preserve">서울숲금고　왕심리중앙지점　　</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  1011 </t>
+          <t xml:space="preserve">02   2292 0894 </t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  1020 </t>
+          <t xml:space="preserve">02   2295 6243 </t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">04709 </t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260826</t>
+          <t xml:space="preserve">20260828</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로１６번길　４２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　성동구　무학로６길　５０　（도선동，　성동삼성쉐르빌）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0184502</t>
+          <t xml:space="preserve">0172051</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5826,22 +5826,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">평택원예　고덕함박　　　　　　</t>
+          <t xml:space="preserve">남양주축산농협　　　　　　　　</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  668  9234 </t>
+          <t xml:space="preserve">031  566  1011 </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  668  9235 </t>
+          <t xml:space="preserve">031  566  1020 </t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">18017 </t>
+          <t xml:space="preserve">12284 </t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　평택시　함박산８길　３５，　２０１호　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　남양주시　다산지금로１６번길　４２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158460</t>
+          <t xml:space="preserve">0184502</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5878,32 +5878,32 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북원예　백봉로　　　　　　　</t>
+          <t xml:space="preserve">평택원예　고덕함박　　　　　　</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  239  0060 </t>
+          <t xml:space="preserve">031  668  9234 </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  239  0064 </t>
+          <t xml:space="preserve">031  668  9235 </t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">28448 </t>
+          <t xml:space="preserve">18017 </t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260826</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　흥덕구　백봉로　１７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　평택시　함박산８길　３５，　２０１호　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185307</t>
+          <t xml:space="preserve">0158460</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">광혜원　화랑　　　　　　　　　</t>
+          <t xml:space="preserve">충북원예　백봉로　　　　　　　</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  535  4542 </t>
+          <t xml:space="preserve">043  239  0060 </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  535  4956 </t>
+          <t xml:space="preserve">043  239  0064 </t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">27802 </t>
+          <t xml:space="preserve">28448 </t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　진천군　광혜원면　화랑５길　４２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　흥덕구　백봉로　１７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5972,32 +5972,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458555</t>
+          <t xml:space="preserve">0185307</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">서광주　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광혜원　화랑　　　　　　　　　</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  944  4502 </t>
+          <t xml:space="preserve">043  535  4542 </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  944  4511 </t>
+          <t xml:space="preserve">043  535  4956 </t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">62436 </t>
+          <t xml:space="preserve">27802 </t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　송정로２９번길　３７　（송정동）　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　진천군　광혜원면　화랑５길　４２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458908</t>
+          <t xml:space="preserve">0458555</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6034,22 +6034,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">충무　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서광주　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  663  1348 </t>
+          <t xml:space="preserve">062  944  4502 </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  664  5228 </t>
+          <t xml:space="preserve">062  944  4511 </t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">59733 </t>
+          <t xml:space="preserve">62436 </t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　충무로　６３　（충무동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광산구　송정로２９번길　３７　（송정동）　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458911</t>
+          <t xml:space="preserve">0458908</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6086,22 +6086,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">진남　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충무　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  4080 </t>
+          <t xml:space="preserve">061  663  1348 </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  4085 </t>
+          <t xml:space="preserve">061  664  5228 </t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">59718 </t>
+          <t xml:space="preserve">59733 </t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　좌수영로　３１－１　（광무동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　충무로　６３　（충무동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458940</t>
+          <t xml:space="preserve">0458911</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌수영　　　　　　　　　　　　</t>
+          <t xml:space="preserve">진남　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  1609 </t>
+          <t xml:space="preserve">061  643  4080 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  9577 </t>
+          <t xml:space="preserve">061  643  4085 </t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">59754 </t>
+          <t xml:space="preserve">59718 </t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　버드나무길　５－１　（서교동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　좌수영로　３１－１　（광무동）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458953</t>
+          <t xml:space="preserve">0458940</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6190,22 +6190,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">구봉　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">좌수영　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  1139 </t>
+          <t xml:space="preserve">061  642  1609 </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  9609 </t>
+          <t xml:space="preserve">061  643  9577 </t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">59761 </t>
+          <t xml:space="preserve">59754 </t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　신월로　６６８　（국동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　버드나무길　５－１　（서교동）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458995</t>
+          <t xml:space="preserve">0458953</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6242,22 +6242,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">순천만　　　　　　　　　　　　</t>
+          <t xml:space="preserve">구봉　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  741  0001 </t>
+          <t xml:space="preserve">061  643  1139 </t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  742  4977 </t>
+          <t xml:space="preserve">061  643  9609 </t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">57956 </t>
+          <t xml:space="preserve">59761 </t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　순천시　중앙２길　２２　（장천동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　신월로　６６８　（국동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">0459596</t>
+          <t xml:space="preserve">0458995</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6294,22 +6294,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">영암우리　　　　　　　　　　　</t>
+          <t xml:space="preserve">순천만　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  472  2200 </t>
+          <t xml:space="preserve">061  741  0001 </t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  473  1410 </t>
+          <t xml:space="preserve">061  742  4977 </t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">58405 </t>
+          <t xml:space="preserve">57956 </t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　영암군　금정면　용두로　９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　순천시　중앙２길　２２　（장천동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">0459703</t>
+          <t xml:space="preserve">0459596</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6346,22 +6346,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">백수　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">영암우리　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  351  2550 </t>
+          <t xml:space="preserve">061  472  2200 </t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  351  2551 </t>
+          <t xml:space="preserve">061  473  1410 </t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">57029 </t>
+          <t xml:space="preserve">58405 </t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　영광군　백수읍　백수로　７９８　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　영암군　금정면　용두로　９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0851495</t>
+          <t xml:space="preserve">0459703</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6398,22 +6398,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">공화금고엑스포지점　　　　　　</t>
+          <t xml:space="preserve">백수　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  665  1326 </t>
+          <t xml:space="preserve">061  351  2550 </t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  665  1328 </t>
+          <t xml:space="preserve">061  351  2551 </t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">59723 </t>
+          <t xml:space="preserve">57029 </t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　박람회길　６１　（덕충동，　엑스포힐스테이트１단지）１층　제１０２호　　</t>
+          <t xml:space="preserve">전남광주통합특별시　영광군　백수읍　백수로　７９８　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">0855459</t>
+          <t xml:space="preserve">0851495</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6450,22 +6450,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉성금고마산지점　　　　　　　</t>
+          <t xml:space="preserve">공화금고엑스포지점　　　　　　</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  782  4087 </t>
+          <t xml:space="preserve">061  665  1326 </t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  782  5399 </t>
+          <t xml:space="preserve">061  665  1328 </t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">57617 </t>
+          <t xml:space="preserve">59723 </t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　구례군　마산면　화엄사로　１５１　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　박람회길　６１　（덕충동，　엑스포힐스테이트１단지）１층　제１０２호　　</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">0855462</t>
+          <t xml:space="preserve">0855459</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6502,22 +6502,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉성금고토지지점　　　　　　　</t>
+          <t xml:space="preserve">봉성금고마산지점　　　　　　　</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  781  6774 </t>
+          <t xml:space="preserve">061  782  4087 </t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  781  6863 </t>
+          <t xml:space="preserve">061  782  5399 </t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">57624 </t>
+          <t xml:space="preserve">57617 </t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　구례군　토지면　섬진강대로　５０４９　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　구례군　마산면　화엄사로　１５１　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">0855488</t>
+          <t xml:space="preserve">0855462</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6554,22 +6554,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉성금고광의지점　　　　　　　</t>
+          <t xml:space="preserve">봉성금고토지지점　　　　　　　</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  781  3811 </t>
+          <t xml:space="preserve">061  781  6774 </t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  781  6929 </t>
+          <t xml:space="preserve">061  781  6863 </t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">57611 </t>
+          <t xml:space="preserve">57624 </t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　구례군　광의면　구만제로　３２８　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　구례군　토지면　섬진강대로　５０４９　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">0855514</t>
+          <t xml:space="preserve">0855488</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6606,22 +6606,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">여수한려금고율촌지점　　　　　</t>
+          <t xml:space="preserve">봉성금고광의지점　　　　　　　</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  683  6717 </t>
+          <t xml:space="preserve">061  781  3811 </t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  685  7278 </t>
+          <t xml:space="preserve">061  781  6929 </t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">59602 </t>
+          <t xml:space="preserve">57611 </t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　율촌면　동산개길　１５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　구례군　광의면　구만제로　３２８　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">0863360</t>
+          <t xml:space="preserve">0855514</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌수영금고봉산지점　　　　　　</t>
+          <t xml:space="preserve">여수한려금고율촌지점　　　　　</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  7700 </t>
+          <t xml:space="preserve">061  683  6717 </t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  7703 </t>
+          <t xml:space="preserve">061  685  7278 </t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">59762 </t>
+          <t xml:space="preserve">59602 </t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　대교로　１６－２　（봉산동）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　율촌면　동산개길　１５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">0869131</t>
+          <t xml:space="preserve">0863360</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">영암우리금고　신북지점　　　　</t>
+          <t xml:space="preserve">좌수영금고봉산지점　　　　　　</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  472  1919 </t>
+          <t xml:space="preserve">061  642  7700 </t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  471  1920 </t>
+          <t xml:space="preserve">061  642  7703 </t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">58401 </t>
+          <t xml:space="preserve">59762 </t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　영암군　신북면　황금동１길　８　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　대교로　１６－２　（봉산동）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874692</t>
+          <t xml:space="preserve">0869131</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6762,22 +6762,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">진남새마을금고여천지점　　　　</t>
+          <t xml:space="preserve">영암우리금고　신북지점　　　　</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  682  4080 </t>
+          <t xml:space="preserve">061  472  1919 </t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  682  4085 </t>
+          <t xml:space="preserve">061  471  1920 </t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">59673 </t>
+          <t xml:space="preserve">58401 </t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　도원로　２８３　（학동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　영암군　신북면　황금동１길　８　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0875769</t>
+          <t xml:space="preserve">0874692</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6814,22 +6814,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">서광주금고월곡　　　　　　　　</t>
+          <t xml:space="preserve">진남새마을금고여천지점　　　　</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  951  7450 </t>
+          <t xml:space="preserve">061  682  4080 </t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  953  1114 </t>
+          <t xml:space="preserve">061  682  4085 </t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">62348 </t>
+          <t xml:space="preserve">59673 </t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　월곡산정로　７５－１　（월곡동）　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　도원로　２８３　（학동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">0875772</t>
+          <t xml:space="preserve">0875769</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6866,22 +6866,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">서광주금고첨단　　　　　　　　</t>
+          <t xml:space="preserve">서광주금고월곡　　　　　　　　</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  971  2828 </t>
+          <t xml:space="preserve">062  951  7450 </t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  971  2829 </t>
+          <t xml:space="preserve">062  953  1114 </t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">62266 </t>
+          <t xml:space="preserve">62348 </t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　월계로　１０８　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광산구　월곡산정로　７５－１　（월곡동）　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877194</t>
+          <t xml:space="preserve">0875772</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6918,22 +6918,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌수영금고서교지점　　　　　　</t>
+          <t xml:space="preserve">서광주금고첨단　　　　　　　　</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  641  8036 </t>
+          <t xml:space="preserve">062  971  2828 </t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  641  8026 </t>
+          <t xml:space="preserve">062  971  2829 </t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">59752 </t>
+          <t xml:space="preserve">62266 </t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　좌수영로　２０－１　（서교동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광산구　월계로　１０８　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6955,12 +6955,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878009</t>
+          <t xml:space="preserve">0877194</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6970,22 +6970,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＨＤ현대중공업　ＨＤ건설기계인</t>
+          <t xml:space="preserve">좌수영금고서교지점　　　　　　</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">052  234  6000 </t>
+          <t xml:space="preserve">061  641  8036 </t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">052  234  6020 </t>
+          <t xml:space="preserve">061  641  8026 </t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">22502 </t>
+          <t xml:space="preserve">59752 </t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　제물포구　인중로　４８９　（화수동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　좌수영로　２０－１　（서교동）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7007,47 +7007,47 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113230</t>
+          <t xml:space="preserve">0878009</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">괴산군（지부）　　　　　　　　</t>
+          <t xml:space="preserve">ＨＤ현대중공업　ＨＤ건설기계인</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  833  0321 </t>
+          <t xml:space="preserve">052  234  6000 </t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  833  2309 </t>
+          <t xml:space="preserve">052  234  6020 </t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">28030 </t>
+          <t xml:space="preserve">22502 </t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260824</t>
+          <t xml:space="preserve">20260825</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　괴산군　괴산읍　읍내로５길　８－９　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　제물포구　인중로　４８９　（화수동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118028</t>
+          <t xml:space="preserve">0113230</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7074,22 +7074,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">창동하나로＜출＞　　　　　　　</t>
+          <t xml:space="preserve">괴산군（지부）　　　　　　　　</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7644 </t>
+          <t xml:space="preserve">043  833  0321 </t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7648 </t>
+          <t xml:space="preserve">043  833  2309 </t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">01414 </t>
+          <t xml:space="preserve">28030 </t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　괴산군　괴산읍　읍내로５길　８－９　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7116,32 +7116,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">0812230</t>
+          <t xml:space="preserve">0118028</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">목동금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">창동하나로＜출＞　　　　　　　</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2696 1111 </t>
+          <t xml:space="preserve">02   990  7644 </t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2608 0816 </t>
+          <t xml:space="preserve">02   990  7648 </t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">08000 </t>
+          <t xml:space="preserve">01414 </t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　양천구　오목로　３１５　（목동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7168,32 +7168,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870063</t>
+          <t xml:space="preserve">0812230</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">메리츠증권　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">목동금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  604  6611 </t>
+          <t xml:space="preserve">02   2696 1111 </t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  808  8258 </t>
+          <t xml:space="preserve">02   2608 0816 </t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">47291 </t>
+          <t xml:space="preserve">08000 </t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　해운대구　우동　１４３２，　현대베네시티　제상가동　제２층　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　양천구　오목로　３１５　（목동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7220,45 +7220,97 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t xml:space="preserve">2870063</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메리츠증권　　　　　</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">051  604  6611 </t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">051  808  8258 </t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47291 </t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260824</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부산광역시　해운대구　우동　１４３２，　현대베네시티　제상가동　제２층　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경    </t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2870649</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t xml:space="preserve">메리츠증권　　　　　</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t xml:space="preserve">ＰＩＢ　ＰＲＥＳＴＩＧＥ　센터</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t xml:space="preserve">02   6444 6611 </t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t xml:space="preserve">02   6444 6622 </t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t xml:space="preserve">06021 </t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t xml:space="preserve">20260824</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시　강남구　언주로１５４길　１０　（신사동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>

--- a/src/test/resources/codechgfile.text.xlsx
+++ b/src/test/resources/codechgfile.text.xlsx
@@ -34,7 +34,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -96,42 +96,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0852083</t>
+          <t xml:space="preserve">0185310</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한강금고장승배기지점　　　　　</t>
+          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   822  9712 </t>
+          <t xml:space="preserve">033  255  2325 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   823  4041 </t>
+          <t xml:space="preserve">033  255  2327 </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06925 </t>
+          <t xml:space="preserve">24214 </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260923</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　동작구　상도로　１９５　（노량진동，　힐스테이트　장승배기역）　Ｂ１０５호　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　금호아테라더퍼스트　１０９호　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -143,47 +143,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0901691</t>
+          <t xml:space="preserve">0397137</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">가상자산거래소（코인원）　　　</t>
+          <t xml:space="preserve">하단지점　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6288 6000 </t>
+          <t xml:space="preserve">051  205  2703 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6288 6000 </t>
+          <t xml:space="preserve">051  205  2712 </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">49426 </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260922</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">부산광역시　사하구　낙동남로　１４０４　（하단동）　４층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -195,47 +195,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0065786</t>
+          <t xml:space="preserve">0880783</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">신한　　　　　　　　</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">서초중앙（점）　　　　　　　　</t>
+          <t xml:space="preserve">디지털엑스　（주）　　　　　　</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   598  9282 </t>
+          <t xml:space="preserve">02   1661 9766 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   598  9284 </t>
+          <t xml:space="preserve">02   2139 1123 </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">06641 </t>
+          <t xml:space="preserve">06134 </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　사임당로　８６　（서초동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　테헤란로５길　７　（역삼동）　ＫＧ　타워　４층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -252,42 +252,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0072232</t>
+          <t xml:space="preserve">0900074</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">가락동금융센터　　　　　　　　</t>
+          <t xml:space="preserve">고객서비스　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6425 0961 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   449  0965 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">05699 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　양재대로　９３２，　가락몰　관리업무동　１층　（가락동）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -304,42 +304,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101035</t>
+          <t xml:space="preserve">0900870</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">화정역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">ＣＳ운영　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  973  8100 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  973  8104 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10500 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　덕양구　화신로２６０번길　６６　（화정동）　한빛하이죤　２층　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -356,42 +356,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111083</t>
+          <t xml:space="preserve">0900883</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">남양주시（지부）　　　　　　　</t>
+          <t xml:space="preserve">ＣＳ채널　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  563  5991 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  8524 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로３６번길　２１－２　（다산동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -408,42 +408,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113007</t>
+          <t xml:space="preserve">0900896</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">도안동로　　　　　　　　　　　</t>
+          <t xml:space="preserve">ＣＳ지원　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">042  823  1922 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">042  823  1928 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">34192 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">대전광역시　유성구　원신흥로　１２２－４　（원신흥동）　레이크빌딩　Ｉ，　２층　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -460,42 +460,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135111</t>
+          <t xml:space="preserve">0900906</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">오수관촌　신평　　　　　　　　</t>
+          <t xml:space="preserve">업무지원　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  643  7121 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  643  0065 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">55911 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　임실군　신평면　석등슬치로　３６５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -507,99 +507,99 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233822</t>
+          <t xml:space="preserve">0852083</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">상도동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">한강금고장승배기지점　　　　　</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   823  2261 </t>
+          <t xml:space="preserve">02   822  9712 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   822  3196 </t>
+          <t xml:space="preserve">02   823  4041 </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">156030</t>
+          <t xml:space="preserve">06925 </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260923</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　동작구상도동３２４의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동작구　상도로　１９５　（노량진동，　힐스테이트　장승배기역）　Ｂ１０５호　　　　　　　</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233770</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804248</t>
+          <t xml:space="preserve">0901691</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">운정　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">가상자산거래소（코인원）　　　</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8071 3100 </t>
+          <t xml:space="preserve">02   6288 6000 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8071 3106 </t>
+          <t xml:space="preserve">02   6288 6000 </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260922</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　파주시　와석순환로５１５번길　１０　（와동동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -616,32 +616,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815402</t>
+          <t xml:space="preserve">0065786</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구칠곡금융센터　　　　　　　</t>
+          <t xml:space="preserve">서초중앙（점）　　　　　　　　</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  381  1111 </t>
+          <t xml:space="preserve">02   598  9282 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  311  7020 </t>
+          <t xml:space="preserve">02   598  9284 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">41423 </t>
+          <t xml:space="preserve">06641 </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　북구　학정로　４１９　（동천동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　사임당로　８６　（서초동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -663,37 +663,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2613026</t>
+          <t xml:space="preserve">0072232</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">교보증권　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남고객지원파트　　　　　　　</t>
+          <t xml:space="preserve">가락동금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3771 9000 </t>
+          <t xml:space="preserve">02   6425 0961 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3771 9747 </t>
+          <t xml:space="preserve">02   449  0965 </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">06160 </t>
+          <t xml:space="preserve">05699 </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　테헤란로　４１９　（삼성동）　강남파이낸스플라자２층　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　양재대로　９３２，　가락몰　관리업무동　１층　（가락동）　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -720,32 +720,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2705808</t>
+          <t xml:space="preserve">0101035</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">정자ＷＭ라운지　　　　　　　　</t>
+          <t xml:space="preserve">화정역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  697  7950 </t>
+          <t xml:space="preserve">031  973  8100 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  714  0844 </t>
+          <t xml:space="preserve">031  973  8104 </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">13562 </t>
+          <t xml:space="preserve">10500 </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　정자일로　１００　（정자동，　미켈란쉐르빌），　２층　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　덕양구　화신로２６０번길　６６　（화정동）　한빛하이죤　２층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -772,42 +772,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0137863</t>
+          <t xml:space="preserve">0111083</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">오수관촌　지사　　　　　　　　</t>
+          <t xml:space="preserve">남양주시（지부）　　　　　　　</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  642  4008 </t>
+          <t xml:space="preserve">031  563  5991 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  642  4071 </t>
+          <t xml:space="preserve">031  566  8524 </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">55921 </t>
+          <t xml:space="preserve">12284 </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　임실군　지사면　충효로　２４４２　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　남양주시　다산지금로３６번길　２１－２　（다산동）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -824,42 +824,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0151218</t>
+          <t xml:space="preserve">0113007</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">진주동부　초전　　　　　　　　</t>
+          <t xml:space="preserve">도안동로　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1398 </t>
+          <t xml:space="preserve">042  823  1922 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5687 </t>
+          <t xml:space="preserve">042  823  1928 </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">52739 </t>
+          <t xml:space="preserve">34192 </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대신로　４４７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대전광역시　유성구　원신흥로　１２２－４　（원신흥동）　레이크빌딩　Ｉ，　２층　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -871,47 +871,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808435</t>
+          <t xml:space="preserve">0135111</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">소호대출후선지원팀　　　　　　</t>
+          <t xml:space="preserve">오수관촌　신평　　　　　　　　</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2002 1111 </t>
+          <t xml:space="preserve">063  643  7121 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2002 2553 </t>
+          <t xml:space="preserve">063  643  0065 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">04523 </t>
+          <t xml:space="preserve">55911 </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중구　을지로　３５　（을지로１가）　하나은행　본점　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　임실군　신평면　석등슬치로　３６５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -923,52 +923,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0233822</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">상도동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1926 </t>
+          <t xml:space="preserve">02   823  2261 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">02   822  3196 </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">156030</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260917</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　동작구상도동３２４의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0233770</t>
         </is>
       </c>
     </row>
@@ -980,42 +980,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0851026</t>
+          <t xml:space="preserve">0804248</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청금고가회지점　　　　　　　</t>
+          <t xml:space="preserve">운정　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   747  2670 </t>
+          <t xml:space="preserve">031  8071 3100 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   762  6344 </t>
+          <t xml:space="preserve">031  8071 3106 </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">03056 </t>
+          <t xml:space="preserve">10896 </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260917</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　북촌로　４０　（가회동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　파주시　와석순환로５１５번길　１０　（와동동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1032,42 +1032,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156200</t>
+          <t xml:space="preserve">0815402</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">영남원예　삼방동　　　　　　　</t>
+          <t xml:space="preserve">대구칠곡금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  337  0750 </t>
+          <t xml:space="preserve">053  381  1111 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5931 </t>
+          <t xml:space="preserve">053  311  7020 </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">50815 </t>
+          <t xml:space="preserve">41423 </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260916</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　김해시　삼안로　２５８　화인아파트　상가　１０２호　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　북구　학정로　４１９　（동천동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1084,42 +1084,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185310</t>
+          <t xml:space="preserve">2613026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">교보증권　　　　　　</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
+          <t xml:space="preserve">강남고객지원파트　　　　　　　</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">02   3771 9000 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">02   3771 9747 </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">24214 </t>
+          <t xml:space="preserve">06160 </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　（춘천　아테라더퍼스트）　금호아테라더퍼스트　１０９호</t>
+          <t xml:space="preserve">서울특별시　강남구　테헤란로　４１９　（삼성동）　강남파이낸스플라자２층　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1131,47 +1131,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185323</t>
+          <t xml:space="preserve">2705808</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">안성인삼　매교역　　　　　　　</t>
+          <t xml:space="preserve">정자ＷＭ라운지　　　　　　　　</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  000  0000 </t>
+          <t xml:space="preserve">031  697  7950 </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">031  714  0844 </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">16574 </t>
+          <t xml:space="preserve">13562 </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　효원로　１４６　（세류동，　매교역팰루시드）　근린생활시설　지하　２층　７，</t>
+          <t xml:space="preserve">경기도　성남시　분당구　정자일로　１００　（정자동，　미켈란쉐르빌），　２층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1188,42 +1188,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451044</t>
+          <t xml:space="preserve">0137863</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">오수관촌　지사　　　　　　　　</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   733  2670 </t>
+          <t xml:space="preserve">063  642  4008 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2670 </t>
+          <t xml:space="preserve">063  642  4071 </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">03053 </t>
+          <t xml:space="preserve">55921 </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　삼청로　１０６　（삼청동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　임실군　지사면　충효로　２４４２　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1240,42 +1240,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0151218</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">진주동부　초전　　　　　　　　</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  7926 </t>
+          <t xml:space="preserve">055  755  1398 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">0503 8880 5687 </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">52739 </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대신로　４４７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0808435</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">소호대출후선지원팀　　　　　　</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">02   2002 1111 </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">02   2002 2553 </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">04523 </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　을지로　３５　（을지로１가）　하나은행　본점　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1344,42 +1344,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">0014009</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  240  3700 </t>
+          <t xml:space="preserve">055  755  1926 </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  246  9953 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">48400 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260917</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　남구　문현금융로　２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0014805</t>
+          <t xml:space="preserve">0851026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">삼청금고가회지점　　　　　　　</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  8800 114  </t>
+          <t xml:space="preserve">02   747  2670 </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  8800 0290 </t>
+          <t xml:space="preserve">02   762  6344 </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">22333 </t>
+          <t xml:space="preserve">03056 </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260917</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　제물포구　인항로　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　북촌로　４０　（가회동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1448,42 +1448,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0015008</t>
+          <t xml:space="preserve">0156200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">영남원예　삼방동　　　　　　　</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  2500 114  </t>
+          <t xml:space="preserve">055  337  0750 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  2500 1110 </t>
+          <t xml:space="preserve">0503 8880 5931 </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">16508 </t>
+          <t xml:space="preserve">50815 </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260916</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　센트럴타운로　３５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　김해시　삼안로　２５８　화인아파트　상가　１０２호　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1495,47 +1495,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">0015105</t>
+          <t xml:space="preserve">0185310</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  260  5114 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  267  5605 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">51444 </t>
+          <t xml:space="preserve">24214 </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　성산구　원이대로　６３３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　（춘천　아테라더퍼스트）　금호아테라더퍼스트　１０９호</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1547,47 +1547,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0105141</t>
+          <t xml:space="preserve">0185323</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">화성시　（지부）　　　　　　　</t>
+          <t xml:space="preserve">안성인삼　매교역　　　　　　　</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  369  9000 </t>
+          <t xml:space="preserve">031  000  0000 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  366  7696 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">18270 </t>
+          <t xml:space="preserve">16574 </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　남양읍　시청로１６０번길　４６－１４　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　효원로　１４６　（세류동，　매교역팰루시드）　근린생활시설　지하　２층　７，</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1604,42 +1604,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110932</t>
+          <t xml:space="preserve">0451044</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파금융　　　　　　　　　　　</t>
+          <t xml:space="preserve">삼청　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   404  6546 </t>
+          <t xml:space="preserve">02   733  2670 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   404  9783 </t>
+          <t xml:space="preserve">02   735  2670 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">05702 </t>
+          <t xml:space="preserve">03053 </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　중대로２３길　９　（가락동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　삼청로　１０６　（삼청동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1656,42 +1656,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0350462</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  418  4618 </t>
+          <t xml:space="preserve">055  755  7926 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  418  4625 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">48955 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　해관로　１　（동광동１가），　　　２층　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1703,12 +1703,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878067</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">용인중앙금고　수지금융센터지점</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  895  5200 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  895  5204 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">16871 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　용인시　수지구　현암로　６９　（죽전동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1760,42 +1760,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124407</t>
+          <t xml:space="preserve">0014009</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">조치원　시장　　　　　　　　　</t>
+          <t xml:space="preserve">부산　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">044  865  2461 </t>
+          <t xml:space="preserve">051  240  3700 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 2955 </t>
+          <t xml:space="preserve">051  246  9953 </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">30027 </t>
+          <t xml:space="preserve">48400 </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">세종특별자치시　조치원읍　새내１０길　１２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　남구　문현금융로　２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1812,42 +1812,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0129088</t>
+          <t xml:space="preserve">0014805</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">왕궁농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  832  4008 </t>
+          <t xml:space="preserve">032  8800 114  </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 3597 </t>
+          <t xml:space="preserve">032  8800 0290 </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">54576 </t>
+          <t xml:space="preserve">22333 </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　익산시　왕궁면　흥암１길　２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　제물포구　인항로　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1864,42 +1864,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185284</t>
+          <t xml:space="preserve">0015008</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">남원축협　조산지점　　　　　　</t>
+          <t xml:space="preserve">경기　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  630  1160 </t>
+          <t xml:space="preserve">031  2500 114  </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  000  0000 </t>
+          <t xml:space="preserve">031  2500 1110 </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">55778 </t>
+          <t xml:space="preserve">16508 </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　남원시　요천로　１２７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　센트럴타운로　３５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1916,42 +1916,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0859963</t>
+          <t xml:space="preserve">0015105</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른금고원마루지점　　　　　　</t>
+          <t xml:space="preserve">경남　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  292  0047 </t>
+          <t xml:space="preserve">055  260  5114 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  291  6797 </t>
+          <t xml:space="preserve">055  267  5605 </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">28792 </t>
+          <t xml:space="preserve">51444 </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북　청주시　서원구　월평로　６９　（분평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　성산구　원이대로　６３３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1968,42 +1968,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">0868556</t>
+          <t xml:space="preserve">0105141</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른금고분평지점　　　　　　　</t>
+          <t xml:space="preserve">화성시　（지부）　　　　　　　</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  285  6066 </t>
+          <t xml:space="preserve">031  369  9000 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  283  6066 </t>
+          <t xml:space="preserve">031  366  7696 </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">28799 </t>
+          <t xml:space="preserve">18270 </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　서원구　분평로　３２　（분평동）１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　남양읍　시청로１６０번길　４６－１４　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2020,42 +2020,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0110932</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">송파금융　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1926 </t>
+          <t xml:space="preserve">02   404  6546 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">02   404  9783 </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">05702 </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　중대로２３길　９　（가락동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2072,42 +2072,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0123204</t>
+          <t xml:space="preserve">0350462</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">제주　　　　　　　　</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주농협　　　　　　　　　　</t>
+          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  2481 </t>
+          <t xml:space="preserve">051  418  4618 </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  5188 </t>
+          <t xml:space="preserve">051  418  4625 </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">37116 </t>
+          <t xml:space="preserve">48955 </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　함창읍　함창시장１길　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　해관로　１　（동광동１가），　　　２층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2119,47 +2119,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0131432</t>
+          <t xml:space="preserve">0878067</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">규암　장암　　　　　　　　　　</t>
+          <t xml:space="preserve">용인중앙금고　수지금융센터지점</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  834  2280 </t>
+          <t xml:space="preserve">031  895  5200 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  834  7071 </t>
+          <t xml:space="preserve">031  895  5204 </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">33183 </t>
+          <t xml:space="preserve">16871 </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　부여군　장암면　장암로　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　용인시　수지구　현암로　６９　（죽전동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0138477</t>
+          <t xml:space="preserve">0124407</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2186,32 +2186,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주　은척　　　　　　　　　</t>
+          <t xml:space="preserve">조치원　시장　　　　　　　　　</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  3406 </t>
+          <t xml:space="preserve">044  865  2461 </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  6764 </t>
+          <t xml:space="preserve">0503 8880 2955 </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">37104 </t>
+          <t xml:space="preserve">30027 </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　은척면　성주로　７５４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">세종특별자치시　조치원읍　새내１０길　１２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0138480</t>
+          <t xml:space="preserve">0129088</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주　이안　　　　　　　　　</t>
+          <t xml:space="preserve">왕궁농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  5310 </t>
+          <t xml:space="preserve">063  832  4008 </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  0310 </t>
+          <t xml:space="preserve">0503 8880 3597 </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">37107 </t>
+          <t xml:space="preserve">54576 </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　이안면　양범안룡길　２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　왕궁면　흥암１길　２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156792</t>
+          <t xml:space="preserve">0185284</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2290,32 +2290,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔탄　구장　　　　　　　　　　</t>
+          <t xml:space="preserve">남원축협　조산지점　　　　　　</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  352  8803 </t>
+          <t xml:space="preserve">063  630  1160 </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  352  8126 </t>
+          <t xml:space="preserve">063  000  0000 </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">18529 </t>
+          <t xml:space="preserve">55778 </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　팔탄면　시청로　９３４－５　Ａ동　２０１호　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　남원시　요천로　１２７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2332,42 +2332,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0072850</t>
+          <t xml:space="preserve">0859963</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">청라지점　　　　　　　　　　　</t>
+          <t xml:space="preserve">푸른금고원마루지점　　　　　　</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  569  4960 </t>
+          <t xml:space="preserve">043  292  0047 </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  569  4963 </t>
+          <t xml:space="preserve">043  291  6797 </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">22736 </t>
+          <t xml:space="preserve">28792 </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서해구　청라라임로　７１，　２０４호（청라동，　진영메디피아）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충북　청주시　서원구　월평로　６９　（분평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451028</t>
+          <t xml:space="preserve">0868556</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">광화문　　　　　　　　　　　　</t>
+          <t xml:space="preserve">푸른금고분평지점　　　　　　　</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2188 </t>
+          <t xml:space="preserve">043  285  6066 </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2186 </t>
+          <t xml:space="preserve">043  283  6066 </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">03040 </t>
+          <t xml:space="preserve">28799 </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　자하문로９길　９　（통인동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　서원구　분평로　３２　（분평동）１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0859109</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2446,32 +2446,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">강릉솔향금고교동지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  643  3843 </t>
+          <t xml:space="preserve">055  755  1926 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  643  3369 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">25506 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　강릉시　강릉대로　１４５　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2488,42 +2488,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0032861</t>
+          <t xml:space="preserve">0123204</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">진주상평（지）　　　　　　　　</t>
+          <t xml:space="preserve">북상주농협　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  758  0665 </t>
+          <t xml:space="preserve">054  541  2481 </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0286 </t>
+          <t xml:space="preserve">054  541  5188 </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">52775 </t>
+          <t xml:space="preserve">37116 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대신로　２１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　함창읍　함창시장１길　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2540,42 +2540,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0100816</t>
+          <t xml:space="preserve">0131432</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">메트로팔레스　　　　　　　　　</t>
+          <t xml:space="preserve">규암　장암　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  746  4588 </t>
+          <t xml:space="preserve">041  834  2280 </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  746  4582 </t>
+          <t xml:space="preserve">041  834  7071 </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">42038 </t>
+          <t xml:space="preserve">33183 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　수성구　화랑로　５０　자삼빌딩　１층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　부여군　장암면　장암로　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2592,42 +2592,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101488</t>
+          <t xml:space="preserve">0138477</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">이수역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">북상주　은척　　　　　　　　　</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   599  5731 </t>
+          <t xml:space="preserve">054  541  3406 </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   599  5735 </t>
+          <t xml:space="preserve">054  541  6764 </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">06567 </t>
+          <t xml:space="preserve">37104 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　동작대로　１３２　（방배동），　안석빌딩　１층　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　은척면　성주로　７５４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2644,42 +2644,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110589</t>
+          <t xml:space="preserve">0138480</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">논현남　　　　　　　　　　　　</t>
+          <t xml:space="preserve">북상주　이안　　　　　　　　　</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   561  2836 </t>
+          <t xml:space="preserve">054  541  5310 </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   561  2835 </t>
+          <t xml:space="preserve">054  541  0310 </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">06122 </t>
+          <t xml:space="preserve">37107 </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　봉은사로　１５１　（논현동），　분데스언주　４층　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　이안면　양범안룡길　２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2696,42 +2696,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110725</t>
+          <t xml:space="preserve">0156792</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">면목역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">팔탄　구장　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   494  1596 </t>
+          <t xml:space="preserve">031  352  8803 </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2207 0207 </t>
+          <t xml:space="preserve">031  352  8126 </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">02160 </t>
+          <t xml:space="preserve">18529 </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중랑구　면목로　４３２　（면목동）　３층　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　팔탄면　시청로　９３４－５　Ａ동　２０１호　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2748,42 +2748,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0200732</t>
+          <t xml:space="preserve">0072850</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">영동금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">청라지점　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   546  0911 </t>
+          <t xml:space="preserve">032  569  4960 </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3073 </t>
+          <t xml:space="preserve">032  569  4963 </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">135766</t>
+          <t xml:space="preserve">22736 </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　학동로　４０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서해구　청라라임로　７１，　２０４호（청라동，　진영메디피아）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2800,42 +2800,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0200949</t>
+          <t xml:space="preserve">0451028</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남교보타워금융센터　　　　　</t>
+          <t xml:space="preserve">광화문　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3481 5041 </t>
+          <t xml:space="preserve">02   735  2188 </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3094 </t>
+          <t xml:space="preserve">02   735  2186 </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">137920</t>
+          <t xml:space="preserve">03040 </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　강남대로　４６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　자하문로９길　９　（통인동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2852,42 +2852,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201032</t>
+          <t xml:space="preserve">0859109</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">여의도금융센터　　　　　　　　</t>
+          <t xml:space="preserve">강릉솔향금고교동지점　　　　　</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   785  7100 </t>
+          <t xml:space="preserve">033  643  3843 </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3103 </t>
+          <t xml:space="preserve">033  643  3369 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">150714</t>
+          <t xml:space="preserve">25506 </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로８길　１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　강릉시　강릉대로　１４５　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2904,32 +2904,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201430</t>
+          <t xml:space="preserve">0032861</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">여의도중앙금융센터　　　　　　</t>
+          <t xml:space="preserve">진주상평（지）　　　　　　　　</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   783  4101 </t>
+          <t xml:space="preserve">055  758  0665 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3143 </t>
+          <t xml:space="preserve">0505 075  0286 </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">07327 </t>
+          <t xml:space="preserve">52775 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　여의나루로　７１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대신로　２１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2956,32 +2956,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201980</t>
+          <t xml:space="preserve">0100816</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">사상금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">메트로팔레스　　　　　　　　　</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  322  7200 </t>
+          <t xml:space="preserve">053  746  4588 </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3198 </t>
+          <t xml:space="preserve">053  746  4582 </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">617060</t>
+          <t xml:space="preserve">42038 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　사상구　감전１동　１５２－２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　수성구　화랑로　５０　자삼빌딩　１층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3008,32 +3008,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0202031</t>
+          <t xml:space="preserve">0101488</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">양재중앙금융센터　　　　　　　</t>
+          <t xml:space="preserve">이수역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   589  1900 </t>
+          <t xml:space="preserve">02   599  5731 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3203 </t>
+          <t xml:space="preserve">02   599  5735 </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">137131</t>
+          <t xml:space="preserve">06567 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　양재동　２７５－１외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　동작대로　１３２　（방배동），　안석빌딩　１층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3060,32 +3060,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0205669</t>
+          <t xml:space="preserve">0110589</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">논현남　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2691 2141 </t>
+          <t xml:space="preserve">02   561  2836 </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3566 </t>
+          <t xml:space="preserve">02   561  2835 </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">07714 </t>
+          <t xml:space="preserve">06122 </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강서구　강서로　１７９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　봉은사로　１５１　（논현동），　분데스언주　４층　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0207421</t>
+          <t xml:space="preserve">0110725</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">역삼역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">면목역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   565  8671 </t>
+          <t xml:space="preserve">02   494  1596 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3742 </t>
+          <t xml:space="preserve">02   2207 0207 </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">135080</t>
+          <t xml:space="preserve">02160 </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　역삼동　７２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중랑구　면목로　４３２　（면목동）　３층　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208802</t>
+          <t xml:space="preserve">0200732</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3174,22 +3174,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">교대역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">영동금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   586  2001 </t>
+          <t xml:space="preserve">02   546  0911 </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3880 </t>
+          <t xml:space="preserve">0505 001  3073 </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">137070</t>
+          <t xml:space="preserve">135766</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　서초동　１５７７－４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　학동로　４０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3211,37 +3211,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0501046</t>
+          <t xml:space="preserve">0200949</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">조은　　　　여수（지）　　　　</t>
+          <t xml:space="preserve">강남교보타워금융센터　　　　　</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  660  0114 </t>
+          <t xml:space="preserve">02   3481 5041 </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  666  0107 </t>
+          <t xml:space="preserve">0505 001  3094 </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">59734 </t>
+          <t xml:space="preserve">137920</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　여수시　중앙로　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　강남대로　４６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0500241</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -3268,32 +3268,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877822</t>
+          <t xml:space="preserve">0201032</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">산남금고　중앙지점　　　　　　</t>
+          <t xml:space="preserve">여의도금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  733  2250 </t>
+          <t xml:space="preserve">02   785  7100 </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  733  2252 </t>
+          <t xml:space="preserve">0505 001  3103 </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">63591 </t>
+          <t xml:space="preserve">150714</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　서귀포시　중앙로　４２　（서귀동）　산남금고　중앙지점　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로８길　１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3320,42 +3320,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135360</t>
+          <t xml:space="preserve">0201430</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">북부　율어　　　　　　　　　　</t>
+          <t xml:space="preserve">여의도중앙금융센터　　　　　　</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  852  7013 </t>
+          <t xml:space="preserve">02   783  4101 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  852  7014 </t>
+          <t xml:space="preserve">0505 001  3143 </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">59409 </t>
+          <t xml:space="preserve">07327 </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　보성군　율어면　율어로　５６１　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　여의나루로　７１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3372,42 +3372,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0171816</t>
+          <t xml:space="preserve">0201980</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">고양　원흥　　　　　　　　　　</t>
+          <t xml:space="preserve">사상금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  966  6104 </t>
+          <t xml:space="preserve">051  322  7200 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  967  6114 </t>
+          <t xml:space="preserve">0505 001  3198 </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">10564 </t>
+          <t xml:space="preserve">617060</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　덕양구　권율대로　６７２　１층（원흥역봄오피스텔상가）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산　사상구　감전１동　１５２－２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3424,42 +3424,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233479</t>
+          <t xml:space="preserve">0202031</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
+          <t xml:space="preserve">양재중앙금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  661  7289 </t>
+          <t xml:space="preserve">02   589  1900 </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  661  7082 </t>
+          <t xml:space="preserve">0505 001  3203 </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">48931 </t>
+          <t xml:space="preserve">137131</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　대청로　１３５　（중앙동３가）　７층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　양재동　２７５－１외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3476,42 +3476,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0205669</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">02   2691 2141 </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">0505 001  3566 </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">07714 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강서구　강서로　１７９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3528,42 +3528,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0207421</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">역삼역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">02   565  8671 </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">0505 001  3742 </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">135080</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　역삼동　７２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3580,42 +3580,42 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878038</t>
+          <t xml:space="preserve">0208802</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　금산지점　　　　　</t>
+          <t xml:space="preserve">교대역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  7750 </t>
+          <t xml:space="preserve">02   586  2001 </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  763  3080 </t>
+          <t xml:space="preserve">0505 001  3880 </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">52630 </t>
+          <t xml:space="preserve">137070</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　서초동　１５７７－４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3627,52 +3627,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878041</t>
+          <t xml:space="preserve">0501046</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　대곡지점　　　　　</t>
+          <t xml:space="preserve">조은　　　　여수（지）　　　　</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  744  2690 </t>
+          <t xml:space="preserve">061  660  0114 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  746  7046 </t>
+          <t xml:space="preserve">061  666  0107 </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">52607 </t>
+          <t xml:space="preserve">59734 </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　여수시　중앙로　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0500241</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878054</t>
+          <t xml:space="preserve">0877822</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3694,32 +3694,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　문산지점　　　　　</t>
+          <t xml:space="preserve">산남금고　중앙지점　　　　　　</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  5379 </t>
+          <t xml:space="preserve">064  733  2250 </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  9990 </t>
+          <t xml:space="preserve">064  733  2252 </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">52832 </t>
+          <t xml:space="preserve">63591 </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　서귀포시　중앙로　４２　（서귀동）　산남금고　중앙지점　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3731,47 +3731,47 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233479</t>
+          <t xml:space="preserve">0135360</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
+          <t xml:space="preserve">북부　율어　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2146 6253 </t>
+          <t xml:space="preserve">061  852  7013 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3431 3839 </t>
+          <t xml:space="preserve">061  852  7014 </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">05571 </t>
+          <t xml:space="preserve">59409 </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260903</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　올림픽로４길　４０　（잠실동）　우성　Ｂ상가　１층　ＳＣ제일은행　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　보성군　율어면　율어로　５６１　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124041</t>
+          <t xml:space="preserve">0171816</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3798,32 +3798,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">서하남　감북　　　　　　　　　</t>
+          <t xml:space="preserve">고양　원흥　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   482  0365 </t>
+          <t xml:space="preserve">031  966  6104 </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   482  0367 </t>
+          <t xml:space="preserve">031  967  6114 </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990 </t>
+          <t xml:space="preserve">10564 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　하남시　서하남로　１２４　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　덕양구　권율대로　６７２　１층（원흥역봄오피스텔상가）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3840,42 +3840,42 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124504</t>
+          <t xml:space="preserve">0233479</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">성환농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  581  2911 </t>
+          <t xml:space="preserve">051  661  7289 </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  582  3261 </t>
+          <t xml:space="preserve">051  661  7082 </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">31022 </t>
+          <t xml:space="preserve">48931 </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　성환읍　천안대로　２１２２－１５　２층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　대청로　１３５　（중앙동３가）　７층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3892,42 +3892,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0710934</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울대학교우체국　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   889  0205 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   878  8216 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">08826 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　관악구　관악로　１　（신림동，서울대학교）　두레문예관　６７동　１０５호　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3944,42 +3944,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0720704</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천신북우체국　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  243  9957 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  243  1401 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">24206 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　율문１길　１６－４　（신북읍，춘천신북우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3996,42 +3996,42 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0728913</t>
+          <t xml:space="preserve">0878038</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항대이동우체국　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　금산지점　　　　　</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  278  1921 </t>
+          <t xml:space="preserve">055  761  7750 </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  278  1923 </t>
+          <t xml:space="preserve">055  763  3080 </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">37684 </t>
+          <t xml:space="preserve">52630 </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　남구　대이로４１번길　１８　포항대이동우체국　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4048,42 +4048,42 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0730147</t>
+          <t xml:space="preserve">0878041</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">보은우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　대곡지점　　　　　</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  544  2005 </t>
+          <t xml:space="preserve">055  744  2690 </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  542  3589 </t>
+          <t xml:space="preserve">055  746  7046 </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">28943 </t>
+          <t xml:space="preserve">52607 </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　보은군　보은로　１３５　（보은읍）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4100,42 +4100,42 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0734486</t>
+          <t xml:space="preserve">0878054</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　문산지점　　　　　</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  629  2572 </t>
+          <t xml:space="preserve">055  761  5379 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  622  8975 </t>
+          <t xml:space="preserve">055  761  9990 </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">31158 </t>
+          <t xml:space="preserve">52832 </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　백석３로　１０５　（백석동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4147,47 +4147,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0739371</t>
+          <t xml:space="preserve">0233479</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">신제주우체국　　　　　　　　　</t>
+          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  746  0004 </t>
+          <t xml:space="preserve">02   2146 6253 </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  747  0195 </t>
+          <t xml:space="preserve">02   3431 3839 </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">63122 </t>
+          <t xml:space="preserve">05571 </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260903</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　제주시　선덕로　５　（연동　３１３－４２，　신제주우체국）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로４길　４０　（잠실동）　우성　Ｂ상가　１층　ＳＣ제일은행　　　　　　　　</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4204,32 +4204,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">0740470</t>
+          <t xml:space="preserve">0124041</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">무주무풍우체국　　　　　　　　</t>
+          <t xml:space="preserve">서하남　감북　　　　　　　　　</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  324  4400 </t>
+          <t xml:space="preserve">02   482  0365 </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  324  1630 </t>
+          <t xml:space="preserve">02   482  0367 </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">55559 </t>
+          <t xml:space="preserve">12990 </t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　무주군　현내로　１６５－１０　（무풍면）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　하남시　서하남로　１２４　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4256,32 +4256,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">0741314</t>
+          <t xml:space="preserve">0124504</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">완주상관우체국　　　　　　　　</t>
+          <t xml:space="preserve">성환농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  282  5000 </t>
+          <t xml:space="preserve">041  581  2911 </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  232  0640 </t>
+          <t xml:space="preserve">041  582  3261 </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">55359 </t>
+          <t xml:space="preserve">31022 </t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　완주군　신리로　１０９　（상관면，상관면주민자치센터）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　천안시　서북구　성환읍　천안대로　２１２２－１５　２층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0744159</t>
+          <t xml:space="preserve">0710934</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">돌산우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">서울대학교우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  644  1100 </t>
+          <t xml:space="preserve">02   889  0205 </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  644  1316 </t>
+          <t xml:space="preserve">02   878  8216 </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">59777 </t>
+          <t xml:space="preserve">08826 </t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　방답길　５５－１　（돌산읍，돌산우체국）　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　관악구　관악로　１　（신림동，서울대학교）　두레문예관　６７동　１０５호　　　　　　　　</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">0745860</t>
+          <t xml:space="preserve">0720704</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4370,22 +4370,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">해남마산우체국　　　　　　　　</t>
+          <t xml:space="preserve">춘천신북우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  532  5201 </t>
+          <t xml:space="preserve">033  243  9957 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  534  2654 </t>
+          <t xml:space="preserve">033  243  1401 </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">59020 </t>
+          <t xml:space="preserve">24206 </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　해남군　마산로　４４８　（마산면，해남마산우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　율문１길　１６－４　（신북읍，춘천신북우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0745996</t>
+          <t xml:space="preserve">0728913</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4422,22 +4422,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">도덕우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">포항대이동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  843  0204 </t>
+          <t xml:space="preserve">054  278  1921 </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 005  1865 </t>
+          <t xml:space="preserve">054  278  1923 </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">59546 </t>
+          <t xml:space="preserve">37684 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　고흥군　고흥로　４５３　（도덕면，도덕우체국）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　남구　대이로４１번길　１８　포항대이동우체국　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746296</t>
+          <t xml:space="preserve">0730147</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4474,22 +4474,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">서삼우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">보은우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  394  0214 </t>
+          <t xml:space="preserve">043  544  2005 </t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  393  1391 </t>
+          <t xml:space="preserve">043  542  3589 </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">57232 </t>
+          <t xml:space="preserve">28943 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　장성군　축령로　３６５　（서삼면，서삼우체국）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　보은군　보은로　１３５　（보은읍）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746911</t>
+          <t xml:space="preserve">0734486</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4526,22 +4526,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">여수봉산동우체국　　　　　　　</t>
+          <t xml:space="preserve">천안우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  6105 </t>
+          <t xml:space="preserve">041  629  2572 </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  1305 </t>
+          <t xml:space="preserve">041  622  8975 </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">59763 </t>
+          <t xml:space="preserve">31158 </t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　어항로　３７　（봉산동，여수봉산동우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　천안시　서북구　백석３로　１０５　（백석동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4568,42 +4568,42 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118028</t>
+          <t xml:space="preserve">0739371</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">창동아레나　　　　　　　　　　</t>
+          <t xml:space="preserve">신제주우체국　　　　　　　　　</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7644 </t>
+          <t xml:space="preserve">064  746  0004 </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7648 </t>
+          <t xml:space="preserve">064  747  0195 </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">01414 </t>
+          <t xml:space="preserve">63122 </t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　선덕로　５　（연동　３１３－４２，　신제주우체국）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4620,42 +4620,42 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">0172899</t>
+          <t xml:space="preserve">0740470</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북대구낙농　효자　　　　　　</t>
+          <t xml:space="preserve">무주무풍우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  283  9051 </t>
+          <t xml:space="preserve">063  324  4400 </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  283  9054 </t>
+          <t xml:space="preserve">063  324  1630 </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">37836 </t>
+          <t xml:space="preserve">55559 </t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　남구　효성로　３７　（효자동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　무주군　현내로　１６５－１０　（무풍면）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4672,42 +4672,42 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505576</t>
+          <t xml:space="preserve">0741314</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">라인　　　　영업부　　　　　　</t>
+          <t xml:space="preserve">완주상관우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  223  5506 </t>
+          <t xml:space="preserve">063  282  5000 </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  223  4686 </t>
+          <t xml:space="preserve">063  232  0640 </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">61480 </t>
+          <t xml:space="preserve">55359 </t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　동구　중앙로　１６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　완주군　신리로　１０９　（상관면，상관면주민자치센터）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4719,47 +4719,47 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0644563</t>
+          <t xml:space="preserve">0744159</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">산림조합　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">당진시산림조합수청지점　　　　</t>
+          <t xml:space="preserve">돌산우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  970  2105 </t>
+          <t xml:space="preserve">061  644  1100 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  970  6106 </t>
+          <t xml:space="preserve">061  644  1316 </t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">31817 </t>
+          <t xml:space="preserve">59777 </t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　당진시　수청２로　５２　（수청동）　당진시산림조합수청지점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　방답길　５５－１　（돌산읍，돌산우체국）　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4776,42 +4776,42 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">0030614</t>
+          <t xml:space="preserve">0745860</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">논현역（지）　　　　　　　　　</t>
+          <t xml:space="preserve">해남마산우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   548  4156 </t>
+          <t xml:space="preserve">061  532  5201 </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0061 </t>
+          <t xml:space="preserve">061  534  2654 </t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">06110 </t>
+          <t xml:space="preserve">59020 </t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　강남대로　５６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　해남군　마산로　４４８　（마산면，해남마산우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4828,42 +4828,42 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">0033514</t>
+          <t xml:space="preserve">0745996</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천서해구청역　　　　　　　　</t>
+          <t xml:space="preserve">도덕우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  561  6231 </t>
+          <t xml:space="preserve">061  843  0204 </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0351 </t>
+          <t xml:space="preserve">0505 005  1865 </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">22727 </t>
+          <t xml:space="preserve">59546 </t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서해구　서곶로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　고흥군　고흥로　４５３　（도덕면，도덕우체국）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4880,42 +4880,42 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113654</t>
+          <t xml:space="preserve">0746296</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">익산시（지부）　　　　　　　　</t>
+          <t xml:space="preserve">서삼우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  835  4100 </t>
+          <t xml:space="preserve">061  394  0214 </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  835  5995 </t>
+          <t xml:space="preserve">061  393  1391 </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">54545 </t>
+          <t xml:space="preserve">57232 </t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　익산시　무왕로　１０６９　（영등동）　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　장성군　축령로　３６５　（서삼면，서삼우체국）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4932,42 +4932,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0129101</t>
+          <t xml:space="preserve">0746911</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">광양동부농협　　　　　　　　　</t>
+          <t xml:space="preserve">여수봉산동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  772  2080 </t>
+          <t xml:space="preserve">061  643  6105 </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  772  5885 </t>
+          <t xml:space="preserve">061  642  1305 </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">57712 </t>
+          <t xml:space="preserve">59763 </t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광양시　진월면　선소중앙길　３８　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　어항로　３７　（봉산동，여수봉산동우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4979,245 +4979,245 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451895</t>
+          <t xml:space="preserve">0118028</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">신촌　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">창동아레나　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   393  8275 </t>
+          <t xml:space="preserve">02   990  7644 </t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   364  8275 </t>
+          <t xml:space="preserve">02   990  7648 </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">03776 </t>
+          <t xml:space="preserve">01414 </t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서대문구　연세로　３２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877039</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456272</t>
+          <t xml:space="preserve">0172899</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉산　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북대구낙농　효자　　　　　　</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  424  1628 </t>
+          <t xml:space="preserve">054  283  9051 </t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1629 </t>
+          <t xml:space="preserve">054  283  9054 </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">41959 </t>
+          <t xml:space="preserve">37836 </t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　봉산문화길　２８　봉산새마을금고　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　남구　효성로　３７　（효자동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877152</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456311</t>
+          <t xml:space="preserve">0505576</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">대신　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">라인　　　　영업부　　　　　　</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  3525 </t>
+          <t xml:space="preserve">062  223  5506 </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  0939 </t>
+          <t xml:space="preserve">062  223  4686 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">41927 </t>
+          <t xml:space="preserve">61480 </t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　큰장로２６안길　５　（대신동２６５－５）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　동구　중앙로　１６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877136</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456832</t>
+          <t xml:space="preserve">0644563</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">산림조합　　　　　　</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">불로봉무　　　　　　　　　　　</t>
+          <t xml:space="preserve">당진시산림조합수청지점　　　　</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  983  6037 </t>
+          <t xml:space="preserve">041  970  2105 </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  981  6037 </t>
+          <t xml:space="preserve">041  970  6106 </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">41035 </t>
+          <t xml:space="preserve">31817 </t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　동구　팔공로　１３１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　당진시　수청２로　５２　（수청동）　당진시산림조합수청지점　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877178</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0463773</t>
+          <t xml:space="preserve">0030614</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국인삼공사원주공장　　　　　</t>
+          <t xml:space="preserve">논현역（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  747  3070 </t>
+          <t xml:space="preserve">02   548  4156 </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  747  3959 </t>
+          <t xml:space="preserve">0505 075  0061 </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">26306 </t>
+          <t xml:space="preserve">06110 </t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5227,49 +5227,49 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원　원주시　소초면　북원로　２９５５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　강남대로　５６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877084</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0465755</t>
+          <t xml:space="preserve">0033514</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천서해구청역　　　　　　　　</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  244  0321 </t>
+          <t xml:space="preserve">032  561  6231 </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  244  0302 </t>
+          <t xml:space="preserve">0505 075  0351 </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">37507 </t>
+          <t xml:space="preserve">22727 </t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5279,49 +5279,49 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북　포항시　북구　죽장면　새마을로　３６２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서해구　서곶로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877055</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860114</t>
+          <t xml:space="preserve">0113654</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">대신금고대신지점　　　　　　　</t>
+          <t xml:space="preserve">익산시（지부）　　　　　　　　</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  6833 </t>
+          <t xml:space="preserve">063  835  4100 </t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  6834 </t>
+          <t xml:space="preserve">063  835  5995 </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">41929 </t>
+          <t xml:space="preserve">54545 </t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5331,49 +5331,49 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　달구벌대로　１９５５　（대신동１７５１）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　무왕로　１０６９　（영등동）　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877149</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860923</t>
+          <t xml:space="preserve">0129101</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉산금고중앙지점　　　　　　　</t>
+          <t xml:space="preserve">광양동부농협　　　　　　　　　</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1425 </t>
+          <t xml:space="preserve">061  772  2080 </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1424 </t>
+          <t xml:space="preserve">061  772  5885 </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">41912 </t>
+          <t xml:space="preserve">57712 </t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　교동３길　２３　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광양시　진월면　선소중앙길　３８　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877165</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0866396</t>
+          <t xml:space="preserve">0451895</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5410,22 +5410,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일금고청하지점　　　　　</t>
+          <t xml:space="preserve">신촌　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  232  4931 </t>
+          <t xml:space="preserve">02   393  8275 </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  232  6311 </t>
+          <t xml:space="preserve">02   364  8275 </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">37515 </t>
+          <t xml:space="preserve">03776 </t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북　포항시　북구　청하면　청하로　１９２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서대문구　연세로　３２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877068</t>
+          <t xml:space="preserve">0877039</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0870447</t>
+          <t xml:space="preserve">0456272</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5462,22 +5462,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">불로봉무금고이시아폴리스지점　</t>
+          <t xml:space="preserve">봉산　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  215  7770 </t>
+          <t xml:space="preserve">053  424  1628 </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  984  7627 </t>
+          <t xml:space="preserve">053  422  1629 </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">41026 </t>
+          <t xml:space="preserve">41959 </t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　동구　팔공로５１길　３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　봉산문화길　２８　봉산새마을금고　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0871815</t>
+          <t xml:space="preserve">0877152</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874650</t>
+          <t xml:space="preserve">0456311</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일새마을금고초곡지점　　</t>
+          <t xml:space="preserve">대신　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  261  0301 </t>
+          <t xml:space="preserve">053  252  3525 </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  261  0302 </t>
+          <t xml:space="preserve">053  256  0939 </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">37560 </t>
+          <t xml:space="preserve">41927 </t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5539,24 +5539,24 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　북구　흥해읍　초곡지구로　１０７　포항제일금고　초곡지점　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　큰장로２６안길　５　（대신동２６５－５）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877071</t>
+          <t xml:space="preserve">0877136</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0456832</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　상봉지점　　　　　　</t>
+          <t xml:space="preserve">불로봉무　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">053  983  6037 </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">053  981  6037 </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">41035 </t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5591,24 +5591,24 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　동구　팔공로　１３１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877178</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878038</t>
+          <t xml:space="preserve">0463773</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5618,22 +5618,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　금산지점　　　　　　</t>
+          <t xml:space="preserve">한국인삼공사원주공장　　　　　</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  7750 </t>
+          <t xml:space="preserve">033  747  3070 </t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  763  3080 </t>
+          <t xml:space="preserve">033  747  3959 </t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">52630 </t>
+          <t xml:space="preserve">26306 </t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5643,24 +5643,24 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원　원주시　소초면　북원로　２９５５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877084</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878041</t>
+          <t xml:space="preserve">0465755</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5670,22 +5670,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　대곡지점　　　　　　</t>
+          <t xml:space="preserve">포항제일　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  744  2690 </t>
+          <t xml:space="preserve">054  244  0321 </t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  746  7046 </t>
+          <t xml:space="preserve">054  244  0302 </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">52607 </t>
+          <t xml:space="preserve">37507 </t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5695,24 +5695,24 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북　포항시　북구　죽장면　새마을로　３６２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877055</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878054</t>
+          <t xml:space="preserve">0860114</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5722,22 +5722,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　문산지점　　　　　　</t>
+          <t xml:space="preserve">대신금고대신지점　　　　　　　</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  5379 </t>
+          <t xml:space="preserve">053  252  6833 </t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  9990 </t>
+          <t xml:space="preserve">053  252  6834 </t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">52832 </t>
+          <t xml:space="preserve">41929 </t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　달구벌대로　１９５５　（대신동１７５１）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877149</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878012</t>
+          <t xml:space="preserve">0860923</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5774,240 +5774,240 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울숲금고　왕심리중앙지점　　</t>
+          <t xml:space="preserve">봉산금고중앙지점　　　　　　　</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2292 0894 </t>
+          <t xml:space="preserve">053  422  1425 </t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2295 6243 </t>
+          <t xml:space="preserve">053  422  1424 </t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">04709 </t>
+          <t xml:space="preserve">41912 </t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260828</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　성동구　무학로６길　５０　（도선동，　성동삼성쉐르빌）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　교동３길　２３　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877165</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0172051</t>
+          <t xml:space="preserve">0866396</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">남양주축산농협　　　　　　　　</t>
+          <t xml:space="preserve">포항제일금고청하지점　　　　　</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  1011 </t>
+          <t xml:space="preserve">054  232  4931 </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  1020 </t>
+          <t xml:space="preserve">054  232  6311 </t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">37515 </t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260826</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로１６번길　４２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북　포항시　북구　청하면　청하로　１９２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877068</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0184502</t>
+          <t xml:space="preserve">0870447</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">평택원예　고덕함박　　　　　　</t>
+          <t xml:space="preserve">불로봉무금고이시아폴리스지점　</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  668  9234 </t>
+          <t xml:space="preserve">053  215  7770 </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  668  9235 </t>
+          <t xml:space="preserve">053  984  7627 </t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">18017 </t>
+          <t xml:space="preserve">41026 </t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260826</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　평택시　함박산８길　３５，　２０１호　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　동구　팔공로５１길　３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0871815</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158460</t>
+          <t xml:space="preserve">0874650</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북원예　백봉로　　　　　　　</t>
+          <t xml:space="preserve">포항제일새마을금고초곡지점　　</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  239  0060 </t>
+          <t xml:space="preserve">054  261  0301 </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  239  0064 </t>
+          <t xml:space="preserve">054  261  0302 </t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">28448 </t>
+          <t xml:space="preserve">37560 </t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　흥덕구　백봉로　１７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　북구　흥해읍　초곡지구로　１０７　포항제일금고　초곡지점　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877071</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185307</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">광혜원　화랑　　　　　　　　　</t>
+          <t xml:space="preserve">상봉금고　상봉지점　　　　　　</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  535  4542 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  535  4956 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">27802 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　진천군　광혜원면　화랑５길　４２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458555</t>
+          <t xml:space="preserve">0878038</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6034,32 +6034,32 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">서광주　　　　　　　　　　　　</t>
+          <t xml:space="preserve">상봉금고　금산지점　　　　　　</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  944  4502 </t>
+          <t xml:space="preserve">055  761  7750 </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  944  4511 </t>
+          <t xml:space="preserve">055  763  3080 </t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">62436 </t>
+          <t xml:space="preserve">52630 </t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　송정로２９번길　３７　（송정동）　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6071,12 +6071,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458908</t>
+          <t xml:space="preserve">0878041</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6086,32 +6086,32 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">충무　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">상봉금고　대곡지점　　　　　　</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  663  1348 </t>
+          <t xml:space="preserve">055  744  2690 </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  664  5228 </t>
+          <t xml:space="preserve">055  746  7046 </t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">59733 </t>
+          <t xml:space="preserve">52607 </t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　충무로　６３　（충무동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458911</t>
+          <t xml:space="preserve">0878054</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6138,32 +6138,32 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">진남　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">상봉금고　문산지점　　　　　　</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  4080 </t>
+          <t xml:space="preserve">055  761  5379 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  4085 </t>
+          <t xml:space="preserve">055  761  9990 </t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">59718 </t>
+          <t xml:space="preserve">52832 </t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260831</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　좌수영로　３１－１　（광무동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">0458940</t>
+          <t xml:space="preserve">0878012</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6190,1127 +6190,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌수영　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울숲금고　왕심리중앙지점　　</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  1609 </t>
+          <t xml:space="preserve">02   2292 0894 </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  9577 </t>
+          <t xml:space="preserve">02   2295 6243 </t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">59754 </t>
+          <t xml:space="preserve">04709 </t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260825</t>
+          <t xml:space="preserve">20260828</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　버드나무길　５－１　（서교동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　성동구　무학로６길　５０　（도선동，　성동삼성쉐르빌）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0458953</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구봉　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  643  1139 </t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  643  9609 </t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59761 </t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　신월로　６６８　（국동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0458995</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">순천만　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  741  0001 </t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  742  4977 </t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57956 </t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　순천시　중앙２길　２２　（장천동）　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0459596</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영암우리　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  472  2200 </t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  473  1410 </t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58405 </t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　영암군　금정면　용두로　９　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0459703</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백수　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  351  2550 </t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  351  2551 </t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57029 </t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　영광군　백수읍　백수로　７９８　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0851495</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공화금고엑스포지점　　　　　　</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  665  1326 </t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  665  1328 </t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59723 </t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　박람회길　６１　（덕충동，　엑스포힐스테이트１단지）１층　제１０２호　　</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0855459</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉성금고마산지점　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  782  4087 </t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  782  5399 </t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57617 </t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　구례군　마산면　화엄사로　１５１　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0855462</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉성금고토지지점　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  781  6774 </t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  781  6863 </t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57624 </t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　구례군　토지면　섬진강대로　５０４９　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0855488</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉성금고광의지점　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  781  3811 </t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  781  6929 </t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57611 </t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　구례군　광의면　구만제로　３２８　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0855514</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">여수한려금고율촌지점　　　　　</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  683  6717 </t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  685  7278 </t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59602 </t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　율촌면　동산개길　１５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0863360</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좌수영금고봉산지점　　　　　　</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  642  7700 </t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  642  7703 </t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59762 </t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　대교로　１６－２　（봉산동）　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0869131</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영암우리금고　신북지점　　　　</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  472  1919 </t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  471  1920 </t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58401 </t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　영암군　신북면　황금동１길　８　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0874692</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">진남새마을금고여천지점　　　　</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  682  4080 </t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  682  4085 </t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59673 </t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　도원로　２８３　（학동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0875769</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서광주금고월곡　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  951  7450 </t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  953  1114 </t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62348 </t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　월곡산정로　７５－１　（월곡동）　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0875772</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서광주금고첨단　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  971  2828 </t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062  971  2829 </t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62266 </t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　광산구　월계로　１０８　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0877194</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좌수영금고서교지점　　　　　　</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  641  8036 </t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">061  641  8026 </t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59752 </t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　좌수영로　２０－１　（서교동）　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규    </t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0878009</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ＨＤ현대중공업　ＨＤ건설기계인</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">052  234  6000 </t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">052  234  6020 </t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22502 </t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260825</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인천광역시　제물포구　인중로　４８９　（화수동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0113230</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">괴산군（지부）　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">043  833  0321 </t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">043  833  2309 </t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28030 </t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260824</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">충청북도　괴산군　괴산읍　읍내로５길　８－９　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0118028</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창동하나로＜출＞　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   990  7644 </t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   990  7648 </t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01414 </t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260824</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0812230</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목동금융센터　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   2696 1111 </t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   2608 0816 </t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08000 </t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260824</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서울특별시　양천구　오목로　３１５　（목동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2870063</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">메리츠증권　　　　　</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051  604  6611 </t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051  808  8258 </t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47291 </t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260824</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부산광역시　해운대구　우동　１４３２，　현대베네시티　제상가동　제２층　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       </t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변경    </t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2870649</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">메리츠증권　　　　　</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ＰＩＢ　ＰＲＥＳＴＩＧＥ　센터</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   6444 6611 </t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   6444 6622 </t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06021 </t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260824</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서울특별시　강남구　언주로１５４길　１０　（신사동）　　　　　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>

--- a/src/test/resources/codechgfile.text.xlsx
+++ b/src/test/resources/codechgfile.text.xlsx
@@ -34,7 +34,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J126"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185310</t>
+          <t xml:space="preserve">0131869</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -106,32 +106,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
+          <t xml:space="preserve">두원농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  255  2325 </t>
+          <t xml:space="preserve">061  835  6001 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  255  2327 </t>
+          <t xml:space="preserve">061  835  5008 </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24214 </t>
+          <t xml:space="preserve">59514 </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　금호아테라더퍼스트　１０９호　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　고흥군　두원면　두원로　４６４　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -148,42 +148,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0397137</t>
+          <t xml:space="preserve">0175951</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">하단지점　　　　　　　　　　　</t>
+          <t xml:space="preserve">목포무안신안축협　　　　　　　</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  205  2703 </t>
+          <t xml:space="preserve">061  452  8003 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  205  2712 </t>
+          <t xml:space="preserve">061  453  8234 </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49426 </t>
+          <t xml:space="preserve">58523 </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　사하구　낙동남로　１４０４　（하단동）　４층　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　무안군　무안읍　면성１길　３８－１　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -195,47 +195,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0880783</t>
+          <t xml:space="preserve">0193496</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">신한　　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털엑스　（주）　　　　　　</t>
+          <t xml:space="preserve">여신관리지원센터　　　　　　　</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   1661 9766 </t>
+          <t xml:space="preserve">02   3156 9103 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2139 1123 </t>
+          <t xml:space="preserve">02   3156 9601 </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">06134 </t>
+          <t xml:space="preserve">14239 </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　테헤란로５길　７　（역삼동）　ＫＧ　타워　４층　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　광명시　철산로３０번길　２３　（철산동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -252,42 +252,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0900074</t>
+          <t xml:space="preserve">0198734</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">고객서비스　　　　　　　　　　</t>
+          <t xml:space="preserve">여신관리지원센터대전　　　　　</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1599 3333 </t>
+          <t xml:space="preserve">042  480  6821 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0504 305  9830 </t>
+          <t xml:space="preserve">042  480  6848 </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">34077 </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">대전광역시　유성구　지족로３６４번길　９２　（지족동）　１층　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -304,42 +304,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0900870</t>
+          <t xml:space="preserve">0198747</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＣＳ운영　　　　　　　　　　　</t>
+          <t xml:space="preserve">여신관리지원센터대구　　　　　</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1599 3333 </t>
+          <t xml:space="preserve">053  251  6160 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0504 305  9830 </t>
+          <t xml:space="preserve">053  251  6178 </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">41935 </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">대구광역시　중구　중앙대로　４０１　（남일동），　３층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -356,42 +356,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0900883</t>
+          <t xml:space="preserve">0198750</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＣＳ채널　　　　　　　　　　　</t>
+          <t xml:space="preserve">여신관리지원센터부산　　　　　</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1599 3333 </t>
+          <t xml:space="preserve">051  250  1592 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0504 305  9830 </t>
+          <t xml:space="preserve">051  250  1599 </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">48957 </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　중앙대로　４９　（중앙동２가），　５층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -408,42 +408,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0900896</t>
+          <t xml:space="preserve">0198763</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＣＳ지원　　　　　　　　　　　</t>
+          <t xml:space="preserve">여신관리지원센터광주　　　　　</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1599 3333 </t>
+          <t xml:space="preserve">062  231  6525 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0504 305  9830 </t>
+          <t xml:space="preserve">062  231  6594 </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">62359 </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광산구　사암로　２０５　（우산동）　광산종합금융센터　３층　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -455,47 +455,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0900906</t>
+          <t xml:space="preserve">0377953</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">전북　　　　　　　　</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">업무지원　　　　　　　　　　　</t>
+          <t xml:space="preserve">스트리미　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">     1599 3333 </t>
+          <t xml:space="preserve">02   561  2266 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0504 305  9830 </t>
+          <t xml:space="preserve">070  8282 2845 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">06122 </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260928</t>
+          <t xml:space="preserve">20260930</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　봉은사로　１７９　（논현동）　１２층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -512,42 +512,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0852083</t>
+          <t xml:space="preserve">0185310</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">한강금고장승배기지점　　　　　</t>
+          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   822  9712 </t>
+          <t xml:space="preserve">033  255  2325 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   823  4041 </t>
+          <t xml:space="preserve">033  255  2327 </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">06925 </t>
+          <t xml:space="preserve">24214 </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260923</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　동작구　상도로　１９５　（노량진동，　힐스테이트　장승배기역）　Ｂ１０５호　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　금호아테라더퍼스트　１０９호　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -559,47 +559,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0901691</t>
+          <t xml:space="preserve">0397137</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">카카오뱅크　　　　　</t>
+          <t xml:space="preserve">경남　　　　　　　　</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">가상자산거래소（코인원）　　　</t>
+          <t xml:space="preserve">하단지점　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6288 6000 </t>
+          <t xml:space="preserve">051  205  2703 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6288 6000 </t>
+          <t xml:space="preserve">051  205  2712 </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">13529 </t>
+          <t xml:space="preserve">49426 </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260922</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
+          <t xml:space="preserve">부산광역시　사하구　낙동남로　１４０４　（하단동）　４층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -611,47 +611,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0065786</t>
+          <t xml:space="preserve">0880783</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
+          <t xml:space="preserve">신한　　　　　　　　</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">서초중앙（점）　　　　　　　　</t>
+          <t xml:space="preserve">디지털엑스　（주）　　　　　　</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   598  9282 </t>
+          <t xml:space="preserve">02   1661 9766 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   598  9284 </t>
+          <t xml:space="preserve">02   2139 1123 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">06641 </t>
+          <t xml:space="preserve">06134 </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　사임당로　８６　（서초동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　테헤란로５길　７　（역삼동）　ＫＧ　타워　４층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -668,42 +668,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0072232</t>
+          <t xml:space="preserve">0900074</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">가락동금융센터　　　　　　　　</t>
+          <t xml:space="preserve">고객서비스　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   6425 0961 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   449  0965 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">05699 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　양재대로　９３２，　가락몰　관리업무동　１층　（가락동）　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -720,42 +720,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101035</t>
+          <t xml:space="preserve">0900870</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">화정역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">ＣＳ운영　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  973  8100 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  973  8104 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">10500 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　덕양구　화신로２６０번길　６６　（화정동）　한빛하이죤　２층　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -772,42 +772,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111083</t>
+          <t xml:space="preserve">0900883</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">남양주시（지부）　　　　　　　</t>
+          <t xml:space="preserve">ＣＳ채널　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  563  5991 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  566  8524 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">12284 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　남양주시　다산지금로３６번길　２１－２　（다산동）　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -824,42 +824,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113007</t>
+          <t xml:space="preserve">0900896</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">도안동로　　　　　　　　　　　</t>
+          <t xml:space="preserve">ＣＳ지원　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">042  823  1922 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">042  823  1928 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">34192 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">대전광역시　유성구　원신흥로　１２２－４　（원신흥동）　레이크빌딩　Ｉ，　２층　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -876,42 +876,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135111</t>
+          <t xml:space="preserve">0900906</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">오수관촌　신평　　　　　　　　</t>
+          <t xml:space="preserve">업무지원　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  643  7121 </t>
+          <t xml:space="preserve">     1599 3333 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  643  0065 </t>
+          <t xml:space="preserve">0504 305  9830 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55911 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260928</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　임실군　신평면　석등슬치로　３６５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -923,99 +923,99 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233822</t>
+          <t xml:space="preserve">0852083</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">상도동（지）　　　　　　　　　</t>
+          <t xml:space="preserve">한강금고장승배기지점　　　　　</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   823  2261 </t>
+          <t xml:space="preserve">02   822  9712 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   822  3196 </t>
+          <t xml:space="preserve">02   823  4041 </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">156030</t>
+          <t xml:space="preserve">06925 </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260923</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　동작구상도동３２４의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　동작구　상도로　１９５　（노량진동，　힐스테이트　장승배기역）　Ｂ１０５호　　　　　　　</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233770</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0804248</t>
+          <t xml:space="preserve">0901691</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">카카오뱅크　　　　　</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">운정　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">가상자산거래소（코인원）　　　</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8071 3100 </t>
+          <t xml:space="preserve">02   6288 6000 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  8071 3106 </t>
+          <t xml:space="preserve">02   6288 6000 </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896 </t>
+          <t xml:space="preserve">13529 </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260921</t>
+          <t xml:space="preserve">20260922</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　파주시　와석순환로５１５번길　１０　（와동동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　성남시　분당구　분당내곡로　１３１　（백현동）　판교테크원타워（타워２）　１１층　　　　　　</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1032,32 +1032,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815402</t>
+          <t xml:space="preserve">0065786</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">ＫＢ국민　　　　　　</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구칠곡금융센터　　　　　　　</t>
+          <t xml:space="preserve">서초중앙（점）　　　　　　　　</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  381  1111 </t>
+          <t xml:space="preserve">02   598  9282 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  311  7020 </t>
+          <t xml:space="preserve">02   598  9284 </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">41423 </t>
+          <t xml:space="preserve">06641 </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　북구　학정로　４１９　（동천동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　사임당로　８６　（서초동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1079,37 +1079,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2613026</t>
+          <t xml:space="preserve">0072232</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">교보증권　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남고객지원파트　　　　　　　</t>
+          <t xml:space="preserve">가락동금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3771 9000 </t>
+          <t xml:space="preserve">02   6425 0961 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3771 9747 </t>
+          <t xml:space="preserve">02   449  0965 </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">06160 </t>
+          <t xml:space="preserve">05699 </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　테헤란로　４１９　（삼성동）　강남파이낸스플라자２층　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　양재대로　９３２，　가락몰　관리업무동　１층　（가락동）　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1136,32 +1136,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2705808</t>
+          <t xml:space="preserve">0101035</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나증권　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">정자ＷＭ라운지　　　　　　　　</t>
+          <t xml:space="preserve">화정역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  697  7950 </t>
+          <t xml:space="preserve">031  973  8100 </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  714  0844 </t>
+          <t xml:space="preserve">031  973  8104 </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13562 </t>
+          <t xml:space="preserve">10500 </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　성남시　분당구　정자일로　１００　（정자동，　미켈란쉐르빌），　２층　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　덕양구　화신로２６０번길　６６　（화정동）　한빛하이죤　２층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1188,42 +1188,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0137863</t>
+          <t xml:space="preserve">0111083</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">오수관촌　지사　　　　　　　　</t>
+          <t xml:space="preserve">남양주시（지부）　　　　　　　</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  642  4008 </t>
+          <t xml:space="preserve">031  563  5991 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  642  4071 </t>
+          <t xml:space="preserve">031  566  8524 </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">55921 </t>
+          <t xml:space="preserve">12284 </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　임실군　지사면　충효로　２４４２　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　남양주시　다산지금로３６번길　２１－２　（다산동）　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1240,42 +1240,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0151218</t>
+          <t xml:space="preserve">0113007</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">진주동부　초전　　　　　　　　</t>
+          <t xml:space="preserve">도안동로　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1398 </t>
+          <t xml:space="preserve">042  823  1922 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5687 </t>
+          <t xml:space="preserve">042  823  1928 </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">52739 </t>
+          <t xml:space="preserve">34192 </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대신로　４４７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대전광역시　유성구　원신흥로　１２２－４　（원신흥동）　레이크빌딩　Ｉ，　２층　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808435</t>
+          <t xml:space="preserve">0135111</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">하나　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">소호대출후선지원팀　　　　　　</t>
+          <t xml:space="preserve">오수관촌　신평　　　　　　　　</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2002 1111 </t>
+          <t xml:space="preserve">063  643  7121 </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2002 2553 </t>
+          <t xml:space="preserve">063  643  0065 </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">04523 </t>
+          <t xml:space="preserve">55911 </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260918</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중구　을지로　３５　（을지로１가）　하나은행　본점　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　임실군　신평면　석등슬치로　３６５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1339,52 +1339,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0233822</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">상도동（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1926 </t>
+          <t xml:space="preserve">02   823  2261 </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">02   822  3196 </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">156030</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260917</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　동작구상도동３２４의１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0233770</t>
         </is>
       </c>
     </row>
@@ -1396,42 +1396,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0851026</t>
+          <t xml:space="preserve">0804248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청금고가회지점　　　　　　　</t>
+          <t xml:space="preserve">운정　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   747  2670 </t>
+          <t xml:space="preserve">031  8071 3100 </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   762  6344 </t>
+          <t xml:space="preserve">031  8071 3106 </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">03056 </t>
+          <t xml:space="preserve">10896 </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260917</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　북촌로　４０　（가회동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　파주시　와석순환로５１５번길　１０　（와동동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1448,42 +1448,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156200</t>
+          <t xml:space="preserve">0815402</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">영남원예　삼방동　　　　　　　</t>
+          <t xml:space="preserve">대구칠곡금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  337  0750 </t>
+          <t xml:space="preserve">053  381  1111 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 5931 </t>
+          <t xml:space="preserve">053  311  7020 </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">50815 </t>
+          <t xml:space="preserve">41423 </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260916</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　김해시　삼안로　２５８　화인아파트　상가　１０２호　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　북구　학정로　４１９　（동천동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1500,42 +1500,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185310</t>
+          <t xml:space="preserve">2613026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">교보증권　　　　　　</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
+          <t xml:space="preserve">강남고객지원파트　　　　　　　</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">02   3771 9000 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">02   3771 9747 </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">24214 </t>
+          <t xml:space="preserve">06160 </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　（춘천　아테라더퍼스트）　금호아테라더퍼스트　１０９호</t>
+          <t xml:space="preserve">서울특별시　강남구　테헤란로　４１９　（삼성동）　강남파이낸스플라자２층　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1547,47 +1547,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185323</t>
+          <t xml:space="preserve">2705808</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">하나증권　　　　　　</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">안성인삼　매교역　　　　　　　</t>
+          <t xml:space="preserve">정자ＷＭ라운지　　　　　　　　</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  000  0000 </t>
+          <t xml:space="preserve">031  697  7950 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  000  0000 </t>
+          <t xml:space="preserve">031  714  0844 </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">16574 </t>
+          <t xml:space="preserve">13562 </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260921</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　권선구　효원로　１４６　（세류동，　매교역팰루시드）　근린생활시설　지하　２층　７，</t>
+          <t xml:space="preserve">경기도　성남시　분당구　정자일로　１００　（정자동，　미켈란쉐르빌），　２층　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1604,42 +1604,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451044</t>
+          <t xml:space="preserve">0137863</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">오수관촌　지사　　　　　　　　</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   733  2670 </t>
+          <t xml:space="preserve">063  642  4008 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2670 </t>
+          <t xml:space="preserve">063  642  4071 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">03053 </t>
+          <t xml:space="preserve">55921 </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　삼청로　１０６　（삼청동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　임실군　지사면　충효로　２４４２　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1656,42 +1656,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0151218</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">진주동부　초전　　　　　　　　</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  7926 </t>
+          <t xml:space="preserve">055  755  1398 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">0503 8880 5687 </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">52739 </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대신로　４４７　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1703,47 +1703,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0808435</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">하나　　　　　　　　</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">소호대출후선지원팀　　　　　　</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">02   2002 1111 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">02   2002 2553 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">04523 </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260915</t>
+          <t xml:space="preserve">20260918</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중구　을지로　３５　（을지로１가）　하나은행　본점　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1760,42 +1760,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0014009</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  240  3700 </t>
+          <t xml:space="preserve">055  755  1926 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  246  9953 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">48400 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260917</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　남구　문현금융로　２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1812,42 +1812,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0014805</t>
+          <t xml:space="preserve">0851026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">삼청금고가회지점　　　　　　　</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  8800 114  </t>
+          <t xml:space="preserve">02   747  2670 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  8800 0290 </t>
+          <t xml:space="preserve">02   762  6344 </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">22333 </t>
+          <t xml:space="preserve">03056 </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260917</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　제물포구　인항로　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　북촌로　４０　（가회동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1864,42 +1864,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0015008</t>
+          <t xml:space="preserve">0156200</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">영남원예　삼방동　　　　　　　</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  2500 114  </t>
+          <t xml:space="preserve">055  337  0750 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  2500 1110 </t>
+          <t xml:space="preserve">0503 8880 5931 </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">16508 </t>
+          <t xml:space="preserve">50815 </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260916</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　수원시　영통구　센트럴타운로　３５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　김해시　삼안로　２５８　화인아파트　상가　１０２호　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1911,47 +1911,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0015105</t>
+          <t xml:space="preserve">0185310</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">경남　본부　　　　　　　　　　</t>
+          <t xml:space="preserve">춘천강동　삭주로　　　　　　　</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  260  5114 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  267  5605 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">51444 </t>
+          <t xml:space="preserve">24214 </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　창원시　성산구　원이대로　６３３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　동면　삭주로　２３２　（춘천　아테라더퍼스트）　금호아테라더퍼스트　１０９호</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1963,47 +1963,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">0105141</t>
+          <t xml:space="preserve">0185323</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">화성시　（지부）　　　　　　　</t>
+          <t xml:space="preserve">안성인삼　매교역　　　　　　　</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  369  9000 </t>
+          <t xml:space="preserve">031  000  0000 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  366  7696 </t>
+          <t xml:space="preserve">033  000  0000 </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">18270 </t>
+          <t xml:space="preserve">16574 </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　남양읍　시청로１６０번길　４６－１４　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　권선구　효원로　１４６　（세류동，　매교역팰루시드）　근린생활시설　지하　２층　７，</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2020,42 +2020,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110932</t>
+          <t xml:space="preserve">0451044</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파금융　　　　　　　　　　　</t>
+          <t xml:space="preserve">삼청　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   404  6546 </t>
+          <t xml:space="preserve">02   733  2670 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   404  9783 </t>
+          <t xml:space="preserve">02   735  2670 </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">05702 </t>
+          <t xml:space="preserve">03053 </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　중대로２３길　９　（가락동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　삼청로　１０６　（삼청동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2072,42 +2072,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0350462</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주　　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  418  4618 </t>
+          <t xml:space="preserve">055  755  7926 </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  418  4625 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">48955 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　해관로　１　（동광동１가），　　　２층　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878067</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">용인중앙금고　수지금융센터지점</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  895  5200 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  895  5204 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">16871 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260914</t>
+          <t xml:space="preserve">20260915</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　용인시　수지구　현암로　６９　（죽전동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2176,42 +2176,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124407</t>
+          <t xml:space="preserve">0014009</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">조치원　시장　　　　　　　　　</t>
+          <t xml:space="preserve">부산　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">044  865  2461 </t>
+          <t xml:space="preserve">051  240  3700 </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 2955 </t>
+          <t xml:space="preserve">051  246  9953 </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">30027 </t>
+          <t xml:space="preserve">48400 </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">세종특별자치시　조치원읍　새내１０길　１２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　남구　문현금융로　２５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2228,42 +2228,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0129088</t>
+          <t xml:space="preserve">0014805</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">왕궁농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  832  4008 </t>
+          <t xml:space="preserve">032  8800 114  </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0503 8880 3597 </t>
+          <t xml:space="preserve">032  8800 0290 </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">54576 </t>
+          <t xml:space="preserve">22333 </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　익산시　왕궁면　흥암１길　２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　제물포구　인항로　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2280,42 +2280,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0185284</t>
+          <t xml:space="preserve">0015008</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">남원축협　조산지점　　　　　　</t>
+          <t xml:space="preserve">경기　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  630  1160 </t>
+          <t xml:space="preserve">031  2500 114  </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  000  0000 </t>
+          <t xml:space="preserve">031  2500 1110 </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">55778 </t>
+          <t xml:space="preserve">16508 </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　남원시　요천로　１２７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　수원시　영통구　센트럴타운로　３５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2332,42 +2332,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0859963</t>
+          <t xml:space="preserve">0015105</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">한국　　　　　　　　</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른금고원마루지점　　　　　　</t>
+          <t xml:space="preserve">경남　본부　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  292  0047 </t>
+          <t xml:space="preserve">055  260  5114 </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  291  6797 </t>
+          <t xml:space="preserve">055  267  5605 </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">28792 </t>
+          <t xml:space="preserve">51444 </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">충북　청주시　서원구　월평로　６９　（분평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　창원시　성산구　원이대로　６３３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2384,42 +2384,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0868556</t>
+          <t xml:space="preserve">0105141</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른금고분평지점　　　　　　　</t>
+          <t xml:space="preserve">화성시　（지부）　　　　　　　</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  285  6066 </t>
+          <t xml:space="preserve">031  369  9000 </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  283  6066 </t>
+          <t xml:space="preserve">031  366  7696 </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">28799 </t>
+          <t xml:space="preserve">18270 </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　청주시　서원구　분평로　３２　（분평동）１층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　남양읍　시청로１６０번길　４６－１４　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2436,42 +2436,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0110932</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">송파금융　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  755  1926 </t>
+          <t xml:space="preserve">02   404  6546 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  757  4516 </t>
+          <t xml:space="preserve">02   404  9783 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">05702 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260910</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　중대로２３길　９　（가락동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2488,42 +2488,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0123204</t>
+          <t xml:space="preserve">0350462</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">제주　　　　　　　　</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주농협　　　　　　　　　　</t>
+          <t xml:space="preserve">부산금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  2481 </t>
+          <t xml:space="preserve">051  418  4618 </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  5188 </t>
+          <t xml:space="preserve">051  418  4625 </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">37116 </t>
+          <t xml:space="preserve">48955 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　함창읍　함창시장１길　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　해관로　１　（동광동１가），　　　２층　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2535,47 +2535,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0131432</t>
+          <t xml:space="preserve">0878067</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">규암　장암　　　　　　　　　　</t>
+          <t xml:space="preserve">용인중앙금고　수지금융센터지점</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  834  2280 </t>
+          <t xml:space="preserve">031  895  5200 </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  834  7071 </t>
+          <t xml:space="preserve">031  895  5204 </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">33183 </t>
+          <t xml:space="preserve">16871 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260914</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　부여군　장암면　장암로　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　용인시　수지구　현암로　６９　（죽전동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0138477</t>
+          <t xml:space="preserve">0124407</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2602,32 +2602,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주　은척　　　　　　　　　</t>
+          <t xml:space="preserve">조치원　시장　　　　　　　　　</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  3406 </t>
+          <t xml:space="preserve">044  865  2461 </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  6764 </t>
+          <t xml:space="preserve">0503 8880 2955 </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">37104 </t>
+          <t xml:space="preserve">30027 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　은척면　성주로　７５４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">세종특별자치시　조치원읍　새내１０길　１２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0138480</t>
+          <t xml:space="preserve">0129088</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">북상주　이안　　　　　　　　　</t>
+          <t xml:space="preserve">왕궁농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  5310 </t>
+          <t xml:space="preserve">063  832  4008 </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  541  0310 </t>
+          <t xml:space="preserve">0503 8880 3597 </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">37107 </t>
+          <t xml:space="preserve">54576 </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　상주시　이안면　양범안룡길　２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　왕궁면　흥암１길　２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156792</t>
+          <t xml:space="preserve">0185284</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2706,32 +2706,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔탄　구장　　　　　　　　　　</t>
+          <t xml:space="preserve">남원축협　조산지점　　　　　　</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  352  8803 </t>
+          <t xml:space="preserve">063  630  1160 </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  352  8126 </t>
+          <t xml:space="preserve">063  000  0000 </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">18529 </t>
+          <t xml:space="preserve">55778 </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260909</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　화성시　만세구　팔탄면　시청로　９３４－５　Ａ동　２０１호　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　남원시　요천로　１２７４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2748,42 +2748,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0072850</t>
+          <t xml:space="preserve">0859963</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">수협은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">청라지점　　　　　　　　　　　</t>
+          <t xml:space="preserve">푸른금고원마루지점　　　　　　</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  569  4960 </t>
+          <t xml:space="preserve">043  292  0047 </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  569  4963 </t>
+          <t xml:space="preserve">043  291  6797 </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">22736 </t>
+          <t xml:space="preserve">28792 </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서해구　청라라임로　７１，　２０４호（청라동，　진영메디피아）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충북　청주시　서원구　월평로　６９　（분평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451028</t>
+          <t xml:space="preserve">0868556</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">광화문　　　　　　　　　　　　</t>
+          <t xml:space="preserve">푸른금고분평지점　　　　　　　</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2188 </t>
+          <t xml:space="preserve">043  285  6066 </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   735  2186 </t>
+          <t xml:space="preserve">043  283  6066 </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">03040 </t>
+          <t xml:space="preserve">28799 </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　종로구　자하문로９길　９　（통인동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　청주시　서원구　분평로　３２　（분평동）１층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0859109</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2862,32 +2862,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">강릉솔향금고교동지점　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  643  3843 </t>
+          <t xml:space="preserve">055  755  1926 </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  643  3369 </t>
+          <t xml:space="preserve">055  757  4516 </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">25506 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260908</t>
+          <t xml:space="preserve">20260910</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　강릉시　강릉대로　１４５　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2904,42 +2904,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0032861</t>
+          <t xml:space="preserve">0123204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">진주상평（지）　　　　　　　　</t>
+          <t xml:space="preserve">북상주농협　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  758  0665 </t>
+          <t xml:space="preserve">054  541  2481 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0286 </t>
+          <t xml:space="preserve">054  541  5188 </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">52775 </t>
+          <t xml:space="preserve">37116 </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대신로　２１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　함창읍　함창시장１길　１０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2956,42 +2956,42 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0100816</t>
+          <t xml:space="preserve">0131432</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">메트로팔레스　　　　　　　　　</t>
+          <t xml:space="preserve">규암　장암　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  746  4588 </t>
+          <t xml:space="preserve">041  834  2280 </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  746  4582 </t>
+          <t xml:space="preserve">041  834  7071 </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">42038 </t>
+          <t xml:space="preserve">33183 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구광역시　수성구　화랑로　５０　자삼빌딩　１층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　부여군　장암면　장암로　１４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3008,42 +3008,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101488</t>
+          <t xml:space="preserve">0138477</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">이수역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">북상주　은척　　　　　　　　　</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   599  5731 </t>
+          <t xml:space="preserve">054  541  3406 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   599  5735 </t>
+          <t xml:space="preserve">054  541  6764 </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">06567 </t>
+          <t xml:space="preserve">37104 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　동작대로　１３２　（방배동），　안석빌딩　１층　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　은척면　성주로　７５４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3060,42 +3060,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110589</t>
+          <t xml:space="preserve">0138480</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">논현남　　　　　　　　　　　　</t>
+          <t xml:space="preserve">북상주　이안　　　　　　　　　</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   561  2836 </t>
+          <t xml:space="preserve">054  541  5310 </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   561  2835 </t>
+          <t xml:space="preserve">054  541  0310 </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">06122 </t>
+          <t xml:space="preserve">37107 </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　봉은사로　１５１　（논현동），　분데스언주　４층　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　상주시　이안면　양범안룡길　２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3112,42 +3112,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110725</t>
+          <t xml:space="preserve">0156792</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">면목역　　　　　　　　　　　　</t>
+          <t xml:space="preserve">팔탄　구장　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   494  1596 </t>
+          <t xml:space="preserve">031  352  8803 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2207 0207 </t>
+          <t xml:space="preserve">031  352  8126 </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">02160 </t>
+          <t xml:space="preserve">18529 </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260909</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　중랑구　면목로　４３２　（면목동）　３층　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　화성시　만세구　팔탄면　시청로　９３４－５　Ａ동　２０１호　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3164,42 +3164,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0200732</t>
+          <t xml:space="preserve">0072850</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">수협은행　　　　　　</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">영동금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">청라지점　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   546  0911 </t>
+          <t xml:space="preserve">032  569  4960 </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3073 </t>
+          <t xml:space="preserve">032  569  4963 </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">135766</t>
+          <t xml:space="preserve">22736 </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　학동로　４０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서해구　청라라임로　７１，　２０４호（청라동，　진영메디피아）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0200949</t>
+          <t xml:space="preserve">0451028</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남교보타워금융센터　　　　　</t>
+          <t xml:space="preserve">광화문　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3481 5041 </t>
+          <t xml:space="preserve">02   735  2188 </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3094 </t>
+          <t xml:space="preserve">02   735  2186 </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">137920</t>
+          <t xml:space="preserve">03040 </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　서초구　강남대로　４６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　종로구　자하문로９길　９　（통인동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3268,42 +3268,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201032</t>
+          <t xml:space="preserve">0859109</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">여의도금융센터　　　　　　　　</t>
+          <t xml:space="preserve">강릉솔향금고교동지점　　　　　</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   785  7100 </t>
+          <t xml:space="preserve">033  643  3843 </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3103 </t>
+          <t xml:space="preserve">033  643  3369 </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">150714</t>
+          <t xml:space="preserve">25506 </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260907</t>
+          <t xml:space="preserve">20260908</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　국제금융로８길　１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　강릉시　강릉대로　１４５　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3320,32 +3320,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201430</t>
+          <t xml:space="preserve">0032861</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">여의도중앙금융센터　　　　　　</t>
+          <t xml:space="preserve">진주상평（지）　　　　　　　　</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   783  4101 </t>
+          <t xml:space="preserve">055  758  0665 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3143 </t>
+          <t xml:space="preserve">0505 075  0286 </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">07327 </t>
+          <t xml:space="preserve">52775 </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　영등포구　여의나루로　７１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대신로　２１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3372,32 +3372,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0201980</t>
+          <t xml:space="preserve">0100816</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">사상금융센터　　　　　　　　　</t>
+          <t xml:space="preserve">메트로팔레스　　　　　　　　　</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  322  7200 </t>
+          <t xml:space="preserve">053  746  4588 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3198 </t>
+          <t xml:space="preserve">053  746  4582 </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">617060</t>
+          <t xml:space="preserve">42038 </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산　사상구　감전１동　１５２－２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구광역시　수성구　화랑로　５０　자삼빌딩　１층　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0202031</t>
+          <t xml:space="preserve">0101488</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">양재중앙금융센터　　　　　　　</t>
+          <t xml:space="preserve">이수역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   589  1900 </t>
+          <t xml:space="preserve">02   599  5731 </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3203 </t>
+          <t xml:space="preserve">02   599  5735 </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">137131</t>
+          <t xml:space="preserve">06567 </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　양재동　２７５－１외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　동작대로　１３２　（방배동），　안석빌딩　１층　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3476,32 +3476,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0205669</t>
+          <t xml:space="preserve">0110589</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">논현남　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2691 2141 </t>
+          <t xml:space="preserve">02   561  2836 </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3566 </t>
+          <t xml:space="preserve">02   561  2835 </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">07714 </t>
+          <t xml:space="preserve">06122 </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강서구　강서로　１７９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　봉은사로　１５１　（논현동），　분데스언주　４층　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3528,32 +3528,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0207421</t>
+          <t xml:space="preserve">0110725</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리은행　　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">역삼역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">면목역　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   565  8671 </t>
+          <t xml:space="preserve">02   494  1596 </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3742 </t>
+          <t xml:space="preserve">02   2207 0207 </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">135080</t>
+          <t xml:space="preserve">02160 </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　강남구　역삼동　７２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　중랑구　면목로　４３２　（면목동）　３층　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208802</t>
+          <t xml:space="preserve">0200732</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3590,22 +3590,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">교대역금융센터　　　　　　　　</t>
+          <t xml:space="preserve">영동금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   586  2001 </t>
+          <t xml:space="preserve">02   546  0911 </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 001  3880 </t>
+          <t xml:space="preserve">0505 001  3073 </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">137070</t>
+          <t xml:space="preserve">135766</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서초구　서초동　１５７７－４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　학동로　４０１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3627,37 +3627,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0501046</t>
+          <t xml:space="preserve">0200949</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">조은　　　　여수（지）　　　　</t>
+          <t xml:space="preserve">강남교보타워금융센터　　　　　</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  660  0114 </t>
+          <t xml:space="preserve">02   3481 5041 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  666  0107 </t>
+          <t xml:space="preserve">0505 001  3094 </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">59734 </t>
+          <t xml:space="preserve">137920</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라남도　여수시　중앙로　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　서초구　강남대로　４６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0500241</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -3684,32 +3684,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877822</t>
+          <t xml:space="preserve">0201032</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">산남금고　중앙지점　　　　　　</t>
+          <t xml:space="preserve">여의도금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  733  2250 </t>
+          <t xml:space="preserve">02   785  7100 </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  733  2252 </t>
+          <t xml:space="preserve">0505 001  3103 </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">63591 </t>
+          <t xml:space="preserve">150714</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　서귀포시　중앙로　４２　（서귀동）　산남금고　중앙지점　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　국제금융로８길　１１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3736,42 +3736,42 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0135360</t>
+          <t xml:space="preserve">0201430</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">북부　율어　　　　　　　　　　</t>
+          <t xml:space="preserve">여의도중앙금융센터　　　　　　</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  852  7013 </t>
+          <t xml:space="preserve">02   783  4101 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  852  7014 </t>
+          <t xml:space="preserve">0505 001  3143 </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">59409 </t>
+          <t xml:space="preserve">07327 </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　보성군　율어면　율어로　５６１　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　영등포구　여의나루로　７１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3788,42 +3788,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0171816</t>
+          <t xml:space="preserve">0201980</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">고양　원흥　　　　　　　　　　</t>
+          <t xml:space="preserve">사상금융센터　　　　　　　　　</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  966  6104 </t>
+          <t xml:space="preserve">051  322  7200 </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">031  967  6114 </t>
+          <t xml:space="preserve">0505 001  3198 </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">10564 </t>
+          <t xml:space="preserve">617060</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　고양시　덕양구　권율대로　６７２　１층（원흥역봄오피스텔상가）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산　사상구　감전１동　１５２－２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3840,42 +3840,42 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233479</t>
+          <t xml:space="preserve">0202031</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
+          <t xml:space="preserve">양재중앙금융센터　　　　　　　</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  661  7289 </t>
+          <t xml:space="preserve">02   589  1900 </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">051  661  7082 </t>
+          <t xml:space="preserve">0505 001  3203 </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">48931 </t>
+          <t xml:space="preserve">137131</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">부산광역시　중구　대청로　１３５　（중앙동３가）　７층　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　양재동　２７５－１외　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3892,42 +3892,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0468480</t>
+          <t xml:space="preserve">0205669</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
+          <t xml:space="preserve">화곡역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">02   2691 2141 </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">0505 001  3566 </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">52806 </t>
+          <t xml:space="preserve">07714 </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강서구　강서로　１７９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3944,42 +3944,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0207421</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
+          <t xml:space="preserve">역삼역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">02   565  8671 </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">0505 001  3742 </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">135080</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　강남구　역삼동　７２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3996,42 +3996,42 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878038</t>
+          <t xml:space="preserve">0208802</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">우리은행　　　　　　</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　금산지점　　　　　</t>
+          <t xml:space="preserve">교대역금융센터　　　　　　　　</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  7750 </t>
+          <t xml:space="preserve">02   586  2001 </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  763  3080 </t>
+          <t xml:space="preserve">0505 001  3880 </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">52630 </t>
+          <t xml:space="preserve">137070</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서초구　서초동　１５７７－４　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4043,52 +4043,52 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878041</t>
+          <t xml:space="preserve">0501046</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　대곡지점　　　　　</t>
+          <t xml:space="preserve">조은　　　　여수（지）　　　　</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  744  2690 </t>
+          <t xml:space="preserve">061  660  0114 </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  746  7046 </t>
+          <t xml:space="preserve">061  666  0107 </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">52607 </t>
+          <t xml:space="preserve">59734 </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전라남도　여수시　중앙로　２６　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0500241</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878054</t>
+          <t xml:space="preserve">0877822</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4110,32 +4110,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">참진주금고　문산지점　　　　　</t>
+          <t xml:space="preserve">산남금고　중앙지점　　　　　　</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  5379 </t>
+          <t xml:space="preserve">064  733  2250 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  9990 </t>
+          <t xml:space="preserve">064  733  2252 </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">52832 </t>
+          <t xml:space="preserve">63591 </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260904</t>
+          <t xml:space="preserve">20260907</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　서귀포시　중앙로　４２　（서귀동）　산남금고　중앙지점　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4147,47 +4147,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0233479</t>
+          <t xml:space="preserve">0135360</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
+          <t xml:space="preserve">북부　율어　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   2146 6253 </t>
+          <t xml:space="preserve">061  852  7013 </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   3431 3839 </t>
+          <t xml:space="preserve">061  852  7014 </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">05571 </t>
+          <t xml:space="preserve">59409 </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260903</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　송파구　올림픽로４길　４０　（잠실동）　우성　Ｂ상가　１층　ＳＣ제일은행　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　보성군　율어면　율어로　５６１　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124041</t>
+          <t xml:space="preserve">0171816</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4214,32 +4214,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">서하남　감북　　　　　　　　　</t>
+          <t xml:space="preserve">고양　원흥　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   482  0365 </t>
+          <t xml:space="preserve">031  966  6104 </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   482  0367 </t>
+          <t xml:space="preserve">031  967  6114 </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990 </t>
+          <t xml:space="preserve">10564 </t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도　하남시　서하남로　１２４　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　고양시　덕양구　권율대로　６７２　１층（원흥역봄오피스텔상가）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4256,42 +4256,42 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">0124504</t>
+          <t xml:space="preserve">0233479</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">성환농협　　　　　　　　　　　</t>
+          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  581  2911 </t>
+          <t xml:space="preserve">051  661  7289 </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  582  3261 </t>
+          <t xml:space="preserve">051  661  7082 </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">31022 </t>
+          <t xml:space="preserve">48931 </t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　성환읍　천안대로　２１２２－１５　２층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">부산광역시　중구　대청로　１３５　（중앙동３가）　７층　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4308,42 +4308,42 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0710934</t>
+          <t xml:space="preserve">0468480</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울대학교우체국　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   889  0205 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   878  8216 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">08826 </t>
+          <t xml:space="preserve">52806 </t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　관악구　관악로　１　（신림동，서울대학교）　두레문예관　６７동　１０５호　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　솔밭로　９１　（상평동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4360,42 +4360,42 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">0720704</t>
+          <t xml:space="preserve">0878025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘천신북우체국　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　상봉지점　　　　　</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  243  9957 </t>
+          <t xml:space="preserve">055  742  8929 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  243  1401 </t>
+          <t xml:space="preserve">055  748  9423 </t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">24206 </t>
+          <t xml:space="preserve">52748 </t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원특별자치도　춘천시　율문１길　１６－４　（신북읍，춘천신북우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4412,42 +4412,42 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0728913</t>
+          <t xml:space="preserve">0878038</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항대이동우체국　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　금산지점　　　　　</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  278  1921 </t>
+          <t xml:space="preserve">055  761  7750 </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  278  1923 </t>
+          <t xml:space="preserve">055  763  3080 </t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">37684 </t>
+          <t xml:space="preserve">52630 </t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　남구　대이로４１번길　１８　포항대이동우체국　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4464,42 +4464,42 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">0730147</t>
+          <t xml:space="preserve">0878041</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">보은우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　대곡지점　　　　　</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  544  2005 </t>
+          <t xml:space="preserve">055  744  2690 </t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">043  542  3589 </t>
+          <t xml:space="preserve">055  746  7046 </t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">28943 </t>
+          <t xml:space="preserve">52607 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도　보은군　보은로　１３５　（보은읍）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4516,42 +4516,42 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0734486</t>
+          <t xml:space="preserve">0878054</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">참진주금고　문산지점　　　　　</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  629  2572 </t>
+          <t xml:space="preserve">055  761  5379 </t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  622  8975 </t>
+          <t xml:space="preserve">055  761  9990 </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">31158 </t>
+          <t xml:space="preserve">52832 </t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260904</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　천안시　서북구　백석３로　１０５　（백석동）　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4563,47 +4563,47 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">0739371</t>
+          <t xml:space="preserve">0233479</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">ＳＣ제일　　　　　　</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">신제주우체국　　　　　　　　　</t>
+          <t xml:space="preserve">비대면프리미엄지원２　　　　　</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  746  0004 </t>
+          <t xml:space="preserve">02   2146 6253 </t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">064  747  0195 </t>
+          <t xml:space="preserve">02   3431 3839 </t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">63122 </t>
+          <t xml:space="preserve">05571 </t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260902</t>
+          <t xml:space="preserve">20260903</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주특별자치도　제주시　선덕로　５　（연동　３１３－４２，　신제주우체국）　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　송파구　올림픽로４길　４０　（잠실동）　우성　Ｂ상가　１층　ＳＣ제일은행　　　　　　　　</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4620,32 +4620,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">0740470</t>
+          <t xml:space="preserve">0124041</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">무주무풍우체국　　　　　　　　</t>
+          <t xml:space="preserve">서하남　감북　　　　　　　　　</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  324  4400 </t>
+          <t xml:space="preserve">02   482  0365 </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  324  1630 </t>
+          <t xml:space="preserve">02   482  0367 </t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">55559 </t>
+          <t xml:space="preserve">12990 </t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　무주군　현내로　１６５－１０　（무풍면）　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경기도　하남시　서하남로　１２４　２층　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4672,32 +4672,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">0741314</t>
+          <t xml:space="preserve">0124504</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">우체국　　　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">완주상관우체국　　　　　　　　</t>
+          <t xml:space="preserve">성환농협　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  282  5000 </t>
+          <t xml:space="preserve">041  581  2911 </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  232  0640 </t>
+          <t xml:space="preserve">041  582  3261 </t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">55359 </t>
+          <t xml:space="preserve">31022 </t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　완주군　신리로　１０９　（상관면，상관면주민자치센터）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　천안시　서북구　성환읍　천안대로　２１２２－１５　２층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0744159</t>
+          <t xml:space="preserve">0710934</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">돌산우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">서울대학교우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  644  1100 </t>
+          <t xml:space="preserve">02   889  0205 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  644  1316 </t>
+          <t xml:space="preserve">02   878  8216 </t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">59777 </t>
+          <t xml:space="preserve">08826 </t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　방답길　５５－１　（돌산읍，돌산우체국）　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　관악구　관악로　１　（신림동，서울대학교）　두레문예관　６７동　１０５호　　　　　　　　</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">0745860</t>
+          <t xml:space="preserve">0720704</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4786,22 +4786,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">해남마산우체국　　　　　　　　</t>
+          <t xml:space="preserve">춘천신북우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  532  5201 </t>
+          <t xml:space="preserve">033  243  9957 </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  534  2654 </t>
+          <t xml:space="preserve">033  243  1401 </t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">59020 </t>
+          <t xml:space="preserve">24206 </t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　해남군　마산로　４４８　（마산면，해남마산우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원특별자치도　춘천시　율문１길　１６－４　（신북읍，춘천신북우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">0745996</t>
+          <t xml:space="preserve">0728913</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4838,22 +4838,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">도덕우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">포항대이동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  843  0204 </t>
+          <t xml:space="preserve">054  278  1921 </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 005  1865 </t>
+          <t xml:space="preserve">054  278  1923 </t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">59546 </t>
+          <t xml:space="preserve">37684 </t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　고흥군　고흥로　４５３　（도덕면，도덕우체국）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　남구　대이로４１번길　１８　포항대이동우체국　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746296</t>
+          <t xml:space="preserve">0730147</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">서삼우체국　　　　　　　　　　</t>
+          <t xml:space="preserve">보은우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  394  0214 </t>
+          <t xml:space="preserve">043  544  2005 </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  393  1391 </t>
+          <t xml:space="preserve">043  542  3589 </t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">57232 </t>
+          <t xml:space="preserve">28943 </t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　장성군　축령로　３６５　（서삼면，서삼우체국）　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청북도　보은군　보은로　１３５　（보은읍）　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0746911</t>
+          <t xml:space="preserve">0734486</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4942,22 +4942,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">여수봉산동우체국　　　　　　　</t>
+          <t xml:space="preserve">천안우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  643  6105 </t>
+          <t xml:space="preserve">041  629  2572 </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  642  1305 </t>
+          <t xml:space="preserve">041  622  8975 </t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">59763 </t>
+          <t xml:space="preserve">31158 </t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　여수시　어항로　３７　（봉산동，여수봉산동우체국）　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　천안시　서북구　백석３로　１０５　（백석동）　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4984,42 +4984,42 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118028</t>
+          <t xml:space="preserve">0739371</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">창동아레나　　　　　　　　　　</t>
+          <t xml:space="preserve">신제주우체국　　　　　　　　　</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7644 </t>
+          <t xml:space="preserve">064  746  0004 </t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   990  7648 </t>
+          <t xml:space="preserve">064  747  0195 </t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">01414 </t>
+          <t xml:space="preserve">63122 </t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">제주특별자치도　제주시　선덕로　５　（연동　３１３－４２，　신제주우체국）　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5036,42 +5036,42 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">0172899</t>
+          <t xml:space="preserve">0740470</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북대구낙농　효자　　　　　　</t>
+          <t xml:space="preserve">무주무풍우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  283  9051 </t>
+          <t xml:space="preserve">063  324  4400 </t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  283  9054 </t>
+          <t xml:space="preserve">063  324  1630 </t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">37836 </t>
+          <t xml:space="preserve">55559 </t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　남구　효성로　３７　（효자동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　무주군　현내로　１６５－１０　（무풍면）　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5088,42 +5088,42 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505576</t>
+          <t xml:space="preserve">0741314</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">저축은행　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">라인　　　　영업부　　　　　　</t>
+          <t xml:space="preserve">완주상관우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  223  5506 </t>
+          <t xml:space="preserve">063  282  5000 </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">062  223  4686 </t>
+          <t xml:space="preserve">063  232  0640 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">61480 </t>
+          <t xml:space="preserve">55359 </t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시　동구　중앙로　１６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　완주군　신리로　１０９　（상관면，상관면주민자치센터）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5135,47 +5135,47 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0644563</t>
+          <t xml:space="preserve">0744159</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">산림조합　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">당진시산림조합수청지점　　　　</t>
+          <t xml:space="preserve">돌산우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  970  2105 </t>
+          <t xml:space="preserve">061  644  1100 </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">041  970  6106 </t>
+          <t xml:space="preserve">061  644  1316 </t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">31817 </t>
+          <t xml:space="preserve">59777 </t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260901</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청남도　당진시　수청２로　５２　（수청동）　당진시산림조합수청지점　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　방답길　５５－１　（돌산읍，돌산우체국）　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5192,42 +5192,42 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0030614</t>
+          <t xml:space="preserve">0745860</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">논현역（지）　　　　　　　　　</t>
+          <t xml:space="preserve">해남마산우체국　　　　　　　　</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   548  4156 </t>
+          <t xml:space="preserve">061  532  5201 </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0061 </t>
+          <t xml:space="preserve">061  534  2654 </t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">06110 </t>
+          <t xml:space="preserve">59020 </t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시　강남구　강남대로　５６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　해남군　마산로　４４８　（마산면，해남마산우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5244,42 +5244,42 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0033514</t>
+          <t xml:space="preserve">0745996</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">기업　　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천서해구청역　　　　　　　　</t>
+          <t xml:space="preserve">도덕우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">032  561  6231 </t>
+          <t xml:space="preserve">061  843  0204 </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">0505 075  0351 </t>
+          <t xml:space="preserve">0505 005  1865 </t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">22727 </t>
+          <t xml:space="preserve">59546 </t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">인천광역시　서해구　서곶로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　고흥군　고흥로　４５３　（도덕면，도덕우체국）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5296,42 +5296,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">0113654</t>
+          <t xml:space="preserve">0746296</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">익산시（지부）　　　　　　　　</t>
+          <t xml:space="preserve">서삼우체국　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  835  4100 </t>
+          <t xml:space="preserve">061  394  0214 </t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">063  835  5995 </t>
+          <t xml:space="preserve">061  393  1391 </t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">54545 </t>
+          <t xml:space="preserve">57232 </t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">전북특별자치도　익산시　무왕로　１０６９　（영등동）　１층　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　장성군　축령로　３６５　（서삼면，서삼우체국）　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5348,42 +5348,42 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0129101</t>
+          <t xml:space="preserve">0746911</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">농축협　　　　　　　</t>
+          <t xml:space="preserve">우체국　　　　　　　</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">광양동부농협　　　　　　　　　</t>
+          <t xml:space="preserve">여수봉산동우체국　　　　　　　</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  772  2080 </t>
+          <t xml:space="preserve">061  643  6105 </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">061  772  5885 </t>
+          <t xml:space="preserve">061  642  1305 </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">57712 </t>
+          <t xml:space="preserve">59763 </t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260902</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">전남광주통합특별시　광양시　진월면　선소중앙길　３８　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　여수시　어항로　３７　（봉산동，여수봉산동우체국）　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5395,245 +5395,245 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0451895</t>
+          <t xml:space="preserve">0118028</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">신촌　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">창동아레나　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   393  8275 </t>
+          <t xml:space="preserve">02   990  7644 </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">02   364  8275 </t>
+          <t xml:space="preserve">02   990  7648 </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">03776 </t>
+          <t xml:space="preserve">01414 </t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울　서대문구　연세로　３２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　도봉구　노해로　３８１　（창동），　정일프라자　１층　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877039</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456272</t>
+          <t xml:space="preserve">0172899</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉산　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북대구낙농　효자　　　　　　</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  424  1628 </t>
+          <t xml:space="preserve">054  283  9051 </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1629 </t>
+          <t xml:space="preserve">054  283  9054 </t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">41959 </t>
+          <t xml:space="preserve">37836 </t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　봉산문화길　２８　봉산새마을금고　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경상북도　포항시　남구　효성로　３７　（효자동）　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877152</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456311</t>
+          <t xml:space="preserve">0505576</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">저축은행　　　　　　</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">대신　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">라인　　　　영업부　　　　　　</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  3525 </t>
+          <t xml:space="preserve">062  223  5506 </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  256  0939 </t>
+          <t xml:space="preserve">062  223  4686 </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">41927 </t>
+          <t xml:space="preserve">61480 </t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　큰장로２６안길　５　（대신동２６５－５）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">광주광역시　동구　중앙로　１６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877136</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">신규    </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0456832</t>
+          <t xml:space="preserve">0644563</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">산림조합　　　　　　</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">불로봉무　　　　　　　　　　　</t>
+          <t xml:space="preserve">당진시산림조합수청지점　　　　</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  983  6037 </t>
+          <t xml:space="preserve">041  970  2105 </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  981  6037 </t>
+          <t xml:space="preserve">041  970  6106 </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">41035 </t>
+          <t xml:space="preserve">31817 </t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">20260831</t>
+          <t xml:space="preserve">20260901</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　동구　팔공로　１３１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">충청남도　당진시　수청２로　５２　（수청동）　당진시산림조합수청지점　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877178</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">0463773</t>
+          <t xml:space="preserve">0030614</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국인삼공사원주공장　　　　　</t>
+          <t xml:space="preserve">논현역（지）　　　　　　　　　</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  747  3070 </t>
+          <t xml:space="preserve">02   548  4156 </t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">033  747  3959 </t>
+          <t xml:space="preserve">0505 075  0061 </t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">26306 </t>
+          <t xml:space="preserve">06110 </t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5643,49 +5643,49 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">강원　원주시　소초면　북원로　２９５５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울특별시　강남구　강남대로　５６５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877084</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0465755</t>
+          <t xml:space="preserve">0033514</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">기업　　　　　　　　</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천서해구청역　　　　　　　　</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  244  0321 </t>
+          <t xml:space="preserve">032  561  6231 </t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  244  0302 </t>
+          <t xml:space="preserve">0505 075  0351 </t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">37507 </t>
+          <t xml:space="preserve">22727 </t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5695,49 +5695,49 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북　포항시　북구　죽장면　새마을로　３６２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">인천광역시　서해구　서곶로　２９３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877055</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860114</t>
+          <t xml:space="preserve">0113654</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">ＮＨ농협은행　　　　</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">대신금고대신지점　　　　　　　</t>
+          <t xml:space="preserve">익산시（지부）　　　　　　　　</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  6833 </t>
+          <t xml:space="preserve">063  835  4100 </t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  252  6834 </t>
+          <t xml:space="preserve">063  835  5995 </t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">41929 </t>
+          <t xml:space="preserve">54545 </t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5747,49 +5747,49 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　달구벌대로　１９５５　（대신동１７５１）　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전북특별자치도　익산시　무왕로　１０６９　（영등동）　１층　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877149</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐쇄    </t>
+          <t xml:space="preserve">변경    </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0860923</t>
+          <t xml:space="preserve">0129101</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">새마을금고　　　　　</t>
+          <t xml:space="preserve">농축협　　　　　　　</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">봉산금고중앙지점　　　　　　　</t>
+          <t xml:space="preserve">광양동부농협　　　　　　　　　</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1425 </t>
+          <t xml:space="preserve">061  772  2080 </t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  422  1424 </t>
+          <t xml:space="preserve">061  772  5885 </t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">41912 </t>
+          <t xml:space="preserve">57712 </t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　중구　교동３길　２３　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">전남광주통합특별시　광양시　진월면　선소중앙길　３８　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877165</t>
+          <t xml:space="preserve">       </t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0866396</t>
+          <t xml:space="preserve">0451895</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5826,22 +5826,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일금고청하지점　　　　　</t>
+          <t xml:space="preserve">신촌　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  232  4931 </t>
+          <t xml:space="preserve">02   393  8275 </t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  232  6311 </t>
+          <t xml:space="preserve">02   364  8275 </t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">37515 </t>
+          <t xml:space="preserve">03776 </t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">경북　포항시　북구　청하면　청하로　１９２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">서울　서대문구　연세로　３２－１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877068</t>
+          <t xml:space="preserve">0877039</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0870447</t>
+          <t xml:space="preserve">0456272</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5878,22 +5878,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">불로봉무금고이시아폴리스지점　</t>
+          <t xml:space="preserve">봉산　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  215  7770 </t>
+          <t xml:space="preserve">053  424  1628 </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">053  984  7627 </t>
+          <t xml:space="preserve">053  422  1629 </t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">41026 </t>
+          <t xml:space="preserve">41959 </t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">대구　동구　팔공로５１길　３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　봉산문화길　２８　봉산새마을금고　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0871815</t>
+          <t xml:space="preserve">0877152</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0874650</t>
+          <t xml:space="preserve">0456311</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">포항제일새마을금고초곡지점　　</t>
+          <t xml:space="preserve">대신　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  261  0301 </t>
+          <t xml:space="preserve">053  252  3525 </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">054  261  0302 </t>
+          <t xml:space="preserve">053  256  0939 </t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">37560 </t>
+          <t xml:space="preserve">41927 </t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5955,24 +5955,24 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상북도　포항시　북구　흥해읍　초곡지구로　１０７　포항제일금고　초곡지점　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　큰장로２６안길　５　（대신동２６５－５）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0877071</t>
+          <t xml:space="preserve">0877136</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878025</t>
+          <t xml:space="preserve">0456832</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5982,22 +5982,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　상봉지점　　　　　　</t>
+          <t xml:space="preserve">불로봉무　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  742  8929 </t>
+          <t xml:space="preserve">053  983  6037 </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  748  9423 </t>
+          <t xml:space="preserve">053  981  6037 </t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">52748 </t>
+          <t xml:space="preserve">41035 </t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6007,24 +6007,24 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　동구　팔공로　１３１　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877178</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878038</t>
+          <t xml:space="preserve">0463773</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6034,22 +6034,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　금산지점　　　　　　</t>
+          <t xml:space="preserve">한국인삼공사원주공장　　　　　</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  7750 </t>
+          <t xml:space="preserve">033  747  3070 </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  763  3080 </t>
+          <t xml:space="preserve">033  747  3959 </t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">52630 </t>
+          <t xml:space="preserve">26306 </t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6059,24 +6059,24 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">강원　원주시　소초면　북원로　２９５５　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877084</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878041</t>
+          <t xml:space="preserve">0465755</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6086,22 +6086,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　대곡지점　　　　　　</t>
+          <t xml:space="preserve">포항제일　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  744  2690 </t>
+          <t xml:space="preserve">054  244  0321 </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  746  7046 </t>
+          <t xml:space="preserve">054  244  0302 </t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">52607 </t>
+          <t xml:space="preserve">37507 </t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6111,24 +6111,24 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">경북　포항시　북구　죽장면　새마을로　３６２４　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877055</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규    </t>
+          <t xml:space="preserve">폐쇄    </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0878054</t>
+          <t xml:space="preserve">0860114</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">상봉금고　문산지점　　　　　　</t>
+          <t xml:space="preserve">대신금고대신지점　　　　　　　</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  5379 </t>
+          <t xml:space="preserve">053  252  6833 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">055  761  9990 </t>
+          <t xml:space="preserve">053  252  6834 </t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">52832 </t>
+          <t xml:space="preserve">41929 </t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6163,62 +6163,426 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+          <t xml:space="preserve">대구　중구　달구벌대로　１９５５　（대신동１７５１）　　　　　　　　　　　　　　　　　　　　　　　　</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">       </t>
+          <t xml:space="preserve">0877149</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t xml:space="preserve">폐쇄    </t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0860923</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉산금고중앙지점　　　　　　　</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053  422  1425 </t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053  422  1424 </t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41912 </t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대구　중구　교동３길　２３　（교동）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0877165</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐쇄    </t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0866396</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">포항제일금고청하지점　　　　　</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054  232  4931 </t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054  232  6311 </t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37515 </t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경북　포항시　북구　청하면　청하로　１９２　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0877068</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐쇄    </t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0870447</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불로봉무금고이시아폴리스지점　</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053  215  7770 </t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053  984  7627 </t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41026 </t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대구　동구　팔공로５１길　３　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0871815</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐쇄    </t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0874650</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">포항제일새마을금고초곡지점　　</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054  261  0301 </t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054  261  0302 </t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37560 </t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상북도　포항시　북구　흥해읍　초곡지구로　１０７　포항제일금고　초곡지점　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0877071</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t xml:space="preserve">신규    </t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0878012</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0878025</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t xml:space="preserve">새마을금고　　　　　</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서울숲금고　왕심리중앙지점　　</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   2292 0894 </t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02   2295 6243 </t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04709 </t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20260828</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서울특별시　성동구　무학로６길　５０　（도선동，　성동삼성쉐르빌）　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상봉금고　상봉지점　　　　　　</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  742  8929 </t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  748  9423 </t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52748 </t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상남도　진주시　비봉로８１번길　１２　（상봉동）　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규    </t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0878038</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상봉금고　금산지점　　　　　　</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  761  7750 </t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  763  3080 </t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52630 </t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상남도　진주시　금산면　금산로　９９　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규    </t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0878041</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상봉금고　대곡지점　　　　　　</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  744  2690 </t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  746  7046 </t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52607 </t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상남도　진주시　대곡면　남강로２４３８번길　５５　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       </t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규    </t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0878054</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새마을금고　　　　　</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상봉금고　문산지점　　　　　　</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  761  5379 </t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055  761  9990 </t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52832 </t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20260831</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경상남도　진주시　문산읍　월아산로　１０９０　　　　　　　　　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
